--- a/04_Figures/F07_synthesis/modules/c_data/fig1_heatmap.xlsx
+++ b/04_Figures/F07_synthesis/modules/c_data/fig1_heatmap.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">tp</t>
   </si>
@@ -40,9 +40,6 @@
   </si>
   <si>
     <t xml:space="preserve">config</t>
-  </si>
-  <si>
-    <t xml:space="preserve">panel_config</t>
   </si>
   <si>
     <t xml:space="preserve">ME_blue</t>
@@ -135,7 +132,7 @@
     <t xml:space="preserve">bar</t>
   </si>
   <si>
-    <t xml:space="preserve">bar_inner</t>
+    <t xml:space="preserve">n_annotated</t>
   </si>
   <si>
     <t xml:space="preserve">label</t>
@@ -595,14 +592,11 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2"/>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
         <v>15</v>
@@ -620,19 +614,16 @@
         <v>0.0033799153499376</v>
       </c>
       <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
         <v>11</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
         <v>15</v>
@@ -650,19 +641,16 @@
         <v>0.019468555063587</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>14</v>
@@ -680,19 +668,16 @@
         <v>0.0475736718455639</v>
       </c>
       <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
         <v>16</v>
-      </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
         <v>13</v>
@@ -710,19 +695,16 @@
         <v>0.0588097178672731</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>15</v>
@@ -740,19 +722,16 @@
         <v>0.049637741839125</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
         <v>15</v>
@@ -770,19 +749,16 @@
         <v>0.049637741839125</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>14</v>
@@ -800,19 +776,16 @@
         <v>0.181961289717583</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I8" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>15</v>
@@ -830,19 +803,16 @@
         <v>0.049637741839125</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
         <v>14</v>
@@ -860,19 +830,16 @@
         <v>0.11598141379894</v>
       </c>
       <c r="H10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" t="s">
         <v>16</v>
-      </c>
-      <c r="I10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>15</v>
@@ -890,19 +857,16 @@
         <v>0.104252581211931</v>
       </c>
       <c r="H11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" t="s">
         <v>11</v>
-      </c>
-      <c r="I11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
         <v>15</v>
@@ -920,19 +884,16 @@
         <v>0.104252581211931</v>
       </c>
       <c r="H12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" t="s">
         <v>11</v>
-      </c>
-      <c r="I12" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
@@ -950,19 +911,16 @@
         <v>0.217618347262522</v>
       </c>
       <c r="H13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
@@ -980,19 +938,16 @@
         <v>0.21081780193752</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>14</v>
@@ -1010,19 +965,16 @@
         <v>0.42266427323379</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I15" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
@@ -1040,19 +992,16 @@
         <v>0.217618347262522</v>
       </c>
       <c r="H16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I16" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
         <v>15</v>
@@ -1070,19 +1019,16 @@
         <v>0.470770182403954</v>
       </c>
       <c r="H17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" t="s">
         <v>27</v>
-      </c>
-      <c r="I17" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
         <v>15</v>
@@ -1100,19 +1046,16 @@
         <v>0.528044851032142</v>
       </c>
       <c r="H18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I18" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" t="n">
         <v>15</v>
@@ -1130,19 +1073,16 @@
         <v>0.278310804433051</v>
       </c>
       <c r="H19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I19" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
         <v>15</v>
@@ -1160,19 +1100,16 @@
         <v>0.147575075397216</v>
       </c>
       <c r="H20" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" t="s">
         <v>11</v>
-      </c>
-      <c r="I20" t="s">
-        <v>12</v>
-      </c>
-      <c r="J20" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
         <v>14</v>
@@ -1190,19 +1127,16 @@
         <v>0.260909911649474</v>
       </c>
       <c r="H21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I21" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
         <v>14</v>
@@ -1220,19 +1154,16 @@
         <v>0.617693200780729</v>
       </c>
       <c r="H22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" t="n">
         <v>15</v>
@@ -1250,19 +1181,16 @@
         <v>0.574713463742366</v>
       </c>
       <c r="H23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24" t="n">
         <v>15</v>
@@ -1280,19 +1208,16 @@
         <v>0.75624491492708</v>
       </c>
       <c r="H24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I24" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25" t="n">
         <v>15</v>
@@ -1310,19 +1235,16 @@
         <v>0.278310804433051</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I25" t="s">
-        <v>12</v>
-      </c>
-      <c r="J25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" t="n">
         <v>15</v>
@@ -1340,19 +1262,16 @@
         <v>0.471413343185833</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I26" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" t="n">
         <v>13</v>
@@ -1370,19 +1289,16 @@
         <v>0.475916632820825</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I27" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28" t="n">
         <v>15</v>
@@ -1400,19 +1316,16 @@
         <v>0.278310804433051</v>
       </c>
       <c r="H28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I28" t="s">
-        <v>12</v>
-      </c>
-      <c r="J28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" t="n">
         <v>14</v>
@@ -1430,19 +1343,16 @@
         <v>0.260909911649474</v>
       </c>
       <c r="H29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I29" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30" t="n">
         <v>14</v>
@@ -1460,19 +1370,16 @@
         <v>0.713583558071973</v>
       </c>
       <c r="H30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C31" t="n">
         <v>14</v>
@@ -1490,19 +1397,16 @@
         <v>0.816987706248283</v>
       </c>
       <c r="H31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I31" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" t="n">
         <v>14</v>
@@ -1520,19 +1424,16 @@
         <v>0.260909911649474</v>
       </c>
       <c r="H32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I32" t="s">
-        <v>22</v>
-      </c>
-      <c r="J32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" t="n">
         <v>15</v>
@@ -1550,19 +1451,16 @@
         <v>0.349408448229596</v>
       </c>
       <c r="H33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I33" t="s">
-        <v>14</v>
-      </c>
-      <c r="J33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C34" t="n">
         <v>14</v>
@@ -1580,19 +1478,16 @@
         <v>0.364674243618979</v>
       </c>
       <c r="H34" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" t="s">
         <v>16</v>
-      </c>
-      <c r="I34" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C35" t="n">
         <v>15</v>
@@ -1610,19 +1505,16 @@
         <v>0.278310804433051</v>
       </c>
       <c r="H35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I35" t="s">
-        <v>12</v>
-      </c>
-      <c r="J35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C36" t="n">
         <v>15</v>
@@ -1640,19 +1532,16 @@
         <v>0.21975749123208</v>
       </c>
       <c r="H36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I36" t="s">
-        <v>14</v>
-      </c>
-      <c r="J36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37" t="n">
         <v>15</v>
@@ -1670,19 +1559,16 @@
         <v>0.574713463742366</v>
       </c>
       <c r="H37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I37" t="s">
-        <v>28</v>
-      </c>
-      <c r="J37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C38" t="n">
         <v>14</v>
@@ -1700,19 +1586,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I38" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C39" t="n">
         <v>15</v>
@@ -1730,19 +1613,16 @@
         <v>0.610281178434822</v>
       </c>
       <c r="H39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I39" t="s">
-        <v>14</v>
-      </c>
-      <c r="J39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40" t="n">
         <v>14</v>
@@ -1760,19 +1640,16 @@
         <v>0.888598550131416</v>
       </c>
       <c r="H40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I40" t="s">
-        <v>22</v>
-      </c>
-      <c r="J40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C41" t="n">
         <v>15</v>
@@ -1790,19 +1667,16 @@
         <v>0.774291101788778</v>
       </c>
       <c r="H41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I41" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" t="n">
         <v>15</v>
@@ -1820,19 +1694,16 @@
         <v>0.471413343185833</v>
       </c>
       <c r="H42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I42" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C43" t="n">
         <v>14</v>
@@ -1850,19 +1721,16 @@
         <v>0.875502537632114</v>
       </c>
       <c r="H43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I43" t="s">
-        <v>18</v>
-      </c>
-      <c r="J43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" t="n">
         <v>14</v>
@@ -1880,19 +1748,16 @@
         <v>0.737839823018051</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I44" t="s">
-        <v>12</v>
-      </c>
-      <c r="J44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" t="n">
         <v>14</v>
@@ -1910,19 +1775,16 @@
         <v>0.852007703632368</v>
       </c>
       <c r="H45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I45" t="s">
-        <v>22</v>
-      </c>
-      <c r="J45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C46" t="n">
         <v>15</v>
@@ -1940,19 +1802,16 @@
         <v>0.373361990385055</v>
       </c>
       <c r="H46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I46" t="s">
-        <v>14</v>
-      </c>
-      <c r="J46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C47" t="n">
         <v>15</v>
@@ -1970,19 +1829,16 @@
         <v>0.21975749123208</v>
       </c>
       <c r="H47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I47" t="s">
-        <v>14</v>
-      </c>
-      <c r="J47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C48" t="n">
         <v>14</v>
@@ -2000,19 +1856,16 @@
         <v>0.823197435247269</v>
       </c>
       <c r="H48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I48" t="s">
-        <v>28</v>
-      </c>
-      <c r="J48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C49" t="n">
         <v>13</v>
@@ -2030,19 +1883,16 @@
         <v>0.475916632820825</v>
       </c>
       <c r="H49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I49" t="s">
-        <v>22</v>
-      </c>
-      <c r="J49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C50" t="n">
         <v>15</v>
@@ -2060,19 +1910,16 @@
         <v>0.21975749123208</v>
       </c>
       <c r="H50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I50" t="s">
-        <v>14</v>
-      </c>
-      <c r="J50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C51" t="n">
         <v>15</v>
@@ -2090,19 +1937,16 @@
         <v>0.471413343185833</v>
       </c>
       <c r="H51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I51" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C52" t="n">
         <v>15</v>
@@ -2120,19 +1964,16 @@
         <v>0.21975749123208</v>
       </c>
       <c r="H52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I52" t="s">
-        <v>14</v>
-      </c>
-      <c r="J52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53" t="n">
         <v>15</v>
@@ -2150,19 +1991,16 @@
         <v>0.774291101788778</v>
       </c>
       <c r="H53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I53" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C54" t="n">
         <v>13</v>
@@ -2180,19 +2018,16 @@
         <v>0.475916632820825</v>
       </c>
       <c r="H54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I54" t="s">
-        <v>22</v>
-      </c>
-      <c r="J54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C55" t="n">
         <v>14</v>
@@ -2210,19 +2045,16 @@
         <v>0.713583558071973</v>
       </c>
       <c r="H55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I55" t="s">
-        <v>18</v>
-      </c>
-      <c r="J55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C56" t="n">
         <v>15</v>
@@ -2240,19 +2072,16 @@
         <v>0.4945434579341</v>
       </c>
       <c r="H56" t="s">
+        <v>26</v>
+      </c>
+      <c r="I56" t="s">
         <v>27</v>
-      </c>
-      <c r="I56" t="s">
-        <v>28</v>
-      </c>
-      <c r="J56" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C57" t="n">
         <v>13</v>
@@ -2270,19 +2099,16 @@
         <v>0.622814825968136</v>
       </c>
       <c r="H57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I57" t="s">
-        <v>18</v>
-      </c>
-      <c r="J57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C58" t="n">
         <v>15</v>
@@ -2300,19 +2126,16 @@
         <v>0.733535113911462</v>
       </c>
       <c r="H58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I58" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C59" t="n">
         <v>13</v>
@@ -2330,19 +2153,16 @@
         <v>0.475916632820825</v>
       </c>
       <c r="H59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I59" t="s">
-        <v>22</v>
-      </c>
-      <c r="J59" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C60" t="n">
         <v>15</v>
@@ -2360,19 +2180,16 @@
         <v>0.807658284963743</v>
       </c>
       <c r="H60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I60" t="s">
-        <v>28</v>
-      </c>
-      <c r="J60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C61" t="n">
         <v>14</v>
@@ -2390,19 +2207,16 @@
         <v>0.816987706248283</v>
       </c>
       <c r="H61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I61" t="s">
-        <v>22</v>
-      </c>
-      <c r="J61" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" t="n">
         <v>15</v>
@@ -2420,19 +2234,16 @@
         <v>0.4945434579341</v>
       </c>
       <c r="H62" t="s">
+        <v>26</v>
+      </c>
+      <c r="I62" t="s">
         <v>27</v>
-      </c>
-      <c r="I62" t="s">
-        <v>28</v>
-      </c>
-      <c r="J62" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C63" t="n">
         <v>15</v>
@@ -2450,19 +2261,16 @@
         <v>0.4945434579341</v>
       </c>
       <c r="H63" t="s">
+        <v>26</v>
+      </c>
+      <c r="I63" t="s">
         <v>27</v>
-      </c>
-      <c r="I63" t="s">
-        <v>28</v>
-      </c>
-      <c r="J63" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C64" t="n">
         <v>15</v>
@@ -2480,19 +2288,16 @@
         <v>0.471413343185833</v>
       </c>
       <c r="H64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I64" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C65" t="n">
         <v>14</v>
@@ -2510,19 +2315,16 @@
         <v>0.713583558071973</v>
       </c>
       <c r="H65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I65" t="s">
-        <v>18</v>
-      </c>
-      <c r="J65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C66" t="n">
         <v>14</v>
@@ -2540,19 +2342,16 @@
         <v>0.888598550131416</v>
       </c>
       <c r="H66" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I66" t="s">
-        <v>22</v>
-      </c>
-      <c r="J66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C67" t="n">
         <v>14</v>
@@ -2570,19 +2369,16 @@
         <v>0.562228451691707</v>
       </c>
       <c r="H67" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" t="s">
         <v>16</v>
-      </c>
-      <c r="I67" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C68" t="n">
         <v>15</v>
@@ -2600,19 +2396,16 @@
         <v>0.754951971009688</v>
       </c>
       <c r="H68" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I68" t="s">
-        <v>14</v>
-      </c>
-      <c r="J68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C69" t="n">
         <v>15</v>
@@ -2630,19 +2423,16 @@
         <v>0.807658284963743</v>
       </c>
       <c r="H69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I69" t="s">
-        <v>28</v>
-      </c>
-      <c r="J69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C70" t="n">
         <v>15</v>
@@ -2660,19 +2450,16 @@
         <v>0.471413343185833</v>
       </c>
       <c r="H70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I70" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C71" t="n">
         <v>15</v>
@@ -2690,19 +2477,16 @@
         <v>0.823875422930297</v>
       </c>
       <c r="H71" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>12</v>
-      </c>
-      <c r="J71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C72" t="n">
         <v>15</v>
@@ -2720,19 +2504,16 @@
         <v>0.859540943467457</v>
       </c>
       <c r="H72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I72" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C73" t="n">
         <v>14</v>
@@ -2750,19 +2531,16 @@
         <v>0.76627806073437</v>
       </c>
       <c r="H73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I73" t="s">
-        <v>12</v>
-      </c>
-      <c r="J73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C74" t="n">
         <v>15</v>
@@ -2780,19 +2558,16 @@
         <v>0.979844227761598</v>
       </c>
       <c r="H74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I74" t="s">
-        <v>14</v>
-      </c>
-      <c r="J74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C75" t="n">
         <v>15</v>
@@ -2810,19 +2585,16 @@
         <v>0.4945434579341</v>
       </c>
       <c r="H75" t="s">
+        <v>26</v>
+      </c>
+      <c r="I75" t="s">
         <v>27</v>
-      </c>
-      <c r="I75" t="s">
-        <v>28</v>
-      </c>
-      <c r="J75" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C76" t="n">
         <v>15</v>
@@ -2840,19 +2612,16 @@
         <v>0.497485699340426</v>
       </c>
       <c r="H76" t="s">
+        <v>10</v>
+      </c>
+      <c r="I76" t="s">
         <v>11</v>
-      </c>
-      <c r="I76" t="s">
-        <v>12</v>
-      </c>
-      <c r="J76" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77"/>
       <c r="B77" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C77" t="n">
         <v>14</v>
@@ -2870,19 +2639,16 @@
         <v>0.823197435247269</v>
       </c>
       <c r="H77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I77" t="s">
-        <v>28</v>
-      </c>
-      <c r="J77" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C78" t="n">
         <v>14</v>
@@ -2900,19 +2666,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H78" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I78" t="s">
-        <v>22</v>
-      </c>
-      <c r="J78" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C79" t="n">
         <v>15</v>
@@ -2930,19 +2693,16 @@
         <v>0.588887151085524</v>
       </c>
       <c r="H79" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I79" t="s">
-        <v>28</v>
-      </c>
-      <c r="J79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C80" t="n">
         <v>15</v>
@@ -2960,19 +2720,16 @@
         <v>0.588887151085524</v>
       </c>
       <c r="H80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I80" t="s">
-        <v>28</v>
-      </c>
-      <c r="J80" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C81" t="n">
         <v>14</v>
@@ -2990,19 +2747,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H81" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I81" t="s">
-        <v>18</v>
-      </c>
-      <c r="J81" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C82" t="n">
         <v>15</v>
@@ -3020,19 +2774,16 @@
         <v>0.303466247109689</v>
       </c>
       <c r="H82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I82" t="s">
-        <v>14</v>
-      </c>
-      <c r="J82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C83" t="n">
         <v>15</v>
@@ -3050,19 +2801,16 @@
         <v>0.859540943467457</v>
       </c>
       <c r="H83" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I83" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C84" t="n">
         <v>15</v>
@@ -3080,19 +2828,16 @@
         <v>0.774291101788778</v>
       </c>
       <c r="H84" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I84" t="s">
-        <v>17</v>
-      </c>
-      <c r="J84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C85" t="n">
         <v>15</v>
@@ -3110,19 +2855,16 @@
         <v>0.823875422930297</v>
       </c>
       <c r="H85" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I85" t="s">
-        <v>12</v>
-      </c>
-      <c r="J85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C86" t="n">
         <v>15</v>
@@ -3140,19 +2882,16 @@
         <v>0.560004807263186</v>
       </c>
       <c r="H86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I86" t="s">
-        <v>12</v>
-      </c>
-      <c r="J86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C87" t="n">
         <v>15</v>
@@ -3170,19 +2909,16 @@
         <v>0.823875422930297</v>
       </c>
       <c r="H87" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I87" t="s">
-        <v>12</v>
-      </c>
-      <c r="J87" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C88" t="n">
         <v>13</v>
@@ -3200,19 +2936,16 @@
         <v>0.729972569590586</v>
       </c>
       <c r="H88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I88" t="s">
-        <v>18</v>
-      </c>
-      <c r="J88" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C89" t="n">
         <v>14</v>
@@ -3230,19 +2963,16 @@
         <v>0.875502537632114</v>
       </c>
       <c r="H89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I89" t="s">
-        <v>18</v>
-      </c>
-      <c r="J89" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C90" t="n">
         <v>15</v>
@@ -3260,19 +2990,16 @@
         <v>0.497485699340426</v>
       </c>
       <c r="H90" t="s">
+        <v>10</v>
+      </c>
+      <c r="I90" t="s">
         <v>11</v>
-      </c>
-      <c r="I90" t="s">
-        <v>12</v>
-      </c>
-      <c r="J90" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C91" t="n">
         <v>15</v>
@@ -3290,19 +3017,16 @@
         <v>0.708648073909734</v>
       </c>
       <c r="H91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I91" t="s">
-        <v>28</v>
-      </c>
-      <c r="J91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C92" t="n">
         <v>15</v>
@@ -3320,19 +3044,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H92" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I92" t="s">
-        <v>12</v>
-      </c>
-      <c r="J92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C93" t="n">
         <v>15</v>
@@ -3350,19 +3071,16 @@
         <v>0.733535113911462</v>
       </c>
       <c r="H93" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I93" t="s">
-        <v>17</v>
-      </c>
-      <c r="J93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C94" t="n">
         <v>15</v>
@@ -3380,19 +3098,16 @@
         <v>0.4945434579341</v>
       </c>
       <c r="H94" t="s">
+        <v>26</v>
+      </c>
+      <c r="I94" t="s">
         <v>27</v>
-      </c>
-      <c r="I94" t="s">
-        <v>28</v>
-      </c>
-      <c r="J94" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C95" t="n">
         <v>14</v>
@@ -3410,19 +3125,16 @@
         <v>0.623529166722416</v>
       </c>
       <c r="H95" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" t="s">
         <v>16</v>
-      </c>
-      <c r="I95" t="s">
-        <v>17</v>
-      </c>
-      <c r="J95" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C96" t="n">
         <v>14</v>
@@ -3440,19 +3152,16 @@
         <v>0.852007703632368</v>
       </c>
       <c r="H96" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I96" t="s">
-        <v>22</v>
-      </c>
-      <c r="J96" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C97" t="n">
         <v>14</v>
@@ -3470,19 +3179,16 @@
         <v>0.816987706248283</v>
       </c>
       <c r="H97" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I97" t="s">
-        <v>22</v>
-      </c>
-      <c r="J97" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C98" t="n">
         <v>14</v>
@@ -3500,19 +3206,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H98" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I98" t="s">
-        <v>18</v>
-      </c>
-      <c r="J98" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C99" t="n">
         <v>15</v>
@@ -3530,19 +3233,16 @@
         <v>0.708648073909734</v>
       </c>
       <c r="H99" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I99" t="s">
-        <v>28</v>
-      </c>
-      <c r="J99" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C100" t="n">
         <v>15</v>
@@ -3560,19 +3260,16 @@
         <v>0.979844227761598</v>
       </c>
       <c r="H100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I100" t="s">
-        <v>14</v>
-      </c>
-      <c r="J100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C101" t="n">
         <v>15</v>
@@ -3590,19 +3287,16 @@
         <v>0.533308450004438</v>
       </c>
       <c r="H101" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I101" t="s">
-        <v>17</v>
-      </c>
-      <c r="J101" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102">
       <c r="A102"/>
       <c r="B102" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C102" t="n">
         <v>15</v>
@@ -3620,19 +3314,16 @@
         <v>0.4945434579341</v>
       </c>
       <c r="H102" t="s">
+        <v>26</v>
+      </c>
+      <c r="I102" t="s">
         <v>27</v>
-      </c>
-      <c r="I102" t="s">
-        <v>28</v>
-      </c>
-      <c r="J102" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="103">
       <c r="A103"/>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C103" t="n">
         <v>14</v>
@@ -3650,19 +3341,16 @@
         <v>0.868889820465352</v>
       </c>
       <c r="H103" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I103" t="s">
-        <v>18</v>
-      </c>
-      <c r="J103" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104">
       <c r="A104"/>
       <c r="B104" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C104" t="n">
         <v>15</v>
@@ -3680,19 +3368,16 @@
         <v>0.588887151085524</v>
       </c>
       <c r="H104" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I104" t="s">
-        <v>28</v>
-      </c>
-      <c r="J104" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105">
       <c r="A105"/>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C105" t="n">
         <v>15</v>
@@ -3710,19 +3395,16 @@
         <v>0.588887151085524</v>
       </c>
       <c r="H105" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I105" t="s">
-        <v>28</v>
-      </c>
-      <c r="J105" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106">
       <c r="A106"/>
       <c r="B106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C106" t="n">
         <v>15</v>
@@ -3740,19 +3422,16 @@
         <v>0.708648073909734</v>
       </c>
       <c r="H106" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I106" t="s">
-        <v>28</v>
-      </c>
-      <c r="J106" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="107">
       <c r="A107"/>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C107" t="n">
         <v>14</v>
@@ -3770,19 +3449,16 @@
         <v>0.816987706248283</v>
       </c>
       <c r="H107" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I107" t="s">
-        <v>22</v>
-      </c>
-      <c r="J107" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108">
       <c r="A108"/>
       <c r="B108" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C108" t="n">
         <v>15</v>
@@ -3800,19 +3476,16 @@
         <v>0.804050630543897</v>
       </c>
       <c r="H108" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I108" t="s">
-        <v>28</v>
-      </c>
-      <c r="J108" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109">
       <c r="A109"/>
       <c r="B109" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C109" t="n">
         <v>15</v>
@@ -3830,19 +3503,16 @@
         <v>0.848787679919784</v>
       </c>
       <c r="H109" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I109" t="s">
-        <v>12</v>
-      </c>
-      <c r="J109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110">
       <c r="A110"/>
       <c r="B110" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C110" t="n">
         <v>15</v>
@@ -3860,19 +3530,16 @@
         <v>0.807658284963743</v>
       </c>
       <c r="H110" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I110" t="s">
-        <v>28</v>
-      </c>
-      <c r="J110" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111">
       <c r="A111"/>
       <c r="B111" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C111" t="n">
         <v>14</v>
@@ -3890,19 +3557,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H111" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I111" t="s">
-        <v>18</v>
-      </c>
-      <c r="J111" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112">
       <c r="A112"/>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C112" t="n">
         <v>15</v>
@@ -3920,19 +3584,16 @@
         <v>0.708648073909734</v>
       </c>
       <c r="H112" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I112" t="s">
-        <v>28</v>
-      </c>
-      <c r="J112" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113">
       <c r="A113"/>
       <c r="B113" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C113" t="n">
         <v>15</v>
@@ -3950,19 +3611,16 @@
         <v>0.533308450004438</v>
       </c>
       <c r="H113" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I113" t="s">
-        <v>17</v>
-      </c>
-      <c r="J113" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114">
       <c r="A114"/>
       <c r="B114" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C114" t="n">
         <v>15</v>
@@ -3980,19 +3638,16 @@
         <v>0.848787679919784</v>
       </c>
       <c r="H114" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I114" t="s">
-        <v>12</v>
-      </c>
-      <c r="J114" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115">
       <c r="A115"/>
       <c r="B115" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C115" t="n">
         <v>15</v>
@@ -4010,19 +3665,16 @@
         <v>0.804050630543897</v>
       </c>
       <c r="H115" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I115" t="s">
-        <v>28</v>
-      </c>
-      <c r="J115" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="116">
       <c r="A116"/>
       <c r="B116" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C116" t="n">
         <v>15</v>
@@ -4040,19 +3692,16 @@
         <v>0.756051387063227</v>
       </c>
       <c r="H116" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I116" t="s">
-        <v>14</v>
-      </c>
-      <c r="J116" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117"/>
       <c r="B117" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C117" t="n">
         <v>13</v>
@@ -4070,19 +3719,16 @@
         <v>0.729972569590586</v>
       </c>
       <c r="H117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I117" t="s">
-        <v>18</v>
-      </c>
-      <c r="J117" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118">
       <c r="A118"/>
       <c r="B118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C118" t="n">
         <v>15</v>
@@ -4100,19 +3746,16 @@
         <v>0.708648073909734</v>
       </c>
       <c r="H118" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I118" t="s">
-        <v>28</v>
-      </c>
-      <c r="J118" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="119">
       <c r="A119"/>
       <c r="B119" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C119" t="n">
         <v>15</v>
@@ -4130,19 +3773,16 @@
         <v>0.804050630543897</v>
       </c>
       <c r="H119" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I119" t="s">
-        <v>28</v>
-      </c>
-      <c r="J119" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120">
       <c r="A120"/>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C120" t="n">
         <v>15</v>
@@ -4160,19 +3800,16 @@
         <v>0.979753656625192</v>
       </c>
       <c r="H120" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I120" t="s">
-        <v>14</v>
-      </c>
-      <c r="J120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121">
       <c r="A121"/>
       <c r="B121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C121" t="n">
         <v>14</v>
@@ -4190,19 +3827,16 @@
         <v>0.875502537632114</v>
       </c>
       <c r="H121" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I121" t="s">
-        <v>18</v>
-      </c>
-      <c r="J121" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="122">
       <c r="A122"/>
       <c r="B122" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C122" t="n">
         <v>14</v>
@@ -4220,19 +3854,16 @@
         <v>0.823197435247269</v>
       </c>
       <c r="H122" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I122" t="s">
-        <v>28</v>
-      </c>
-      <c r="J122" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="123">
       <c r="A123"/>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C123" t="n">
         <v>15</v>
@@ -4250,19 +3881,16 @@
         <v>0.733535113911462</v>
       </c>
       <c r="H123" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I123" t="s">
-        <v>17</v>
-      </c>
-      <c r="J123" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124">
       <c r="A124"/>
       <c r="B124" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C124" t="n">
         <v>15</v>
@@ -4280,19 +3908,16 @@
         <v>0.807658284963743</v>
       </c>
       <c r="H124" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I124" t="s">
-        <v>28</v>
-      </c>
-      <c r="J124" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="125">
       <c r="A125"/>
       <c r="B125" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C125" t="n">
         <v>14</v>
@@ -4310,19 +3935,16 @@
         <v>0.888598550131416</v>
       </c>
       <c r="H125" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I125" t="s">
-        <v>22</v>
-      </c>
-      <c r="J125" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126">
       <c r="A126"/>
       <c r="B126" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C126" t="n">
         <v>15</v>
@@ -4340,19 +3962,16 @@
         <v>0.979844227761598</v>
       </c>
       <c r="H126" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I126" t="s">
-        <v>14</v>
-      </c>
-      <c r="J126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127">
       <c r="A127"/>
       <c r="B127" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C127" t="n">
         <v>15</v>
@@ -4370,19 +3989,16 @@
         <v>0.774291101788778</v>
       </c>
       <c r="H127" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I127" t="s">
-        <v>17</v>
-      </c>
-      <c r="J127" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128">
       <c r="A128"/>
       <c r="B128" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C128" t="n">
         <v>15</v>
@@ -4400,19 +4016,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H128" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I128" t="s">
-        <v>17</v>
-      </c>
-      <c r="J128" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129">
       <c r="A129"/>
       <c r="B129" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C129" t="n">
         <v>14</v>
@@ -4430,19 +4043,16 @@
         <v>0.869333899732566</v>
       </c>
       <c r="H129" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I129" t="s">
-        <v>14</v>
-      </c>
-      <c r="J129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="130">
       <c r="A130"/>
       <c r="B130" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C130" t="n">
         <v>15</v>
@@ -4460,19 +4070,16 @@
         <v>0.807658284963743</v>
       </c>
       <c r="H130" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I130" t="s">
-        <v>28</v>
-      </c>
-      <c r="J130" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="131">
       <c r="A131"/>
       <c r="B131" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C131" t="n">
         <v>15</v>
@@ -4490,19 +4097,16 @@
         <v>0.622628985316801</v>
       </c>
       <c r="H131" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I131" t="s">
-        <v>12</v>
-      </c>
-      <c r="J131" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132">
       <c r="A132"/>
       <c r="B132" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C132" t="n">
         <v>14</v>
@@ -4520,19 +4124,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H132" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I132" t="s">
-        <v>18</v>
-      </c>
-      <c r="J132" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="133">
       <c r="A133"/>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C133" t="n">
         <v>14</v>
@@ -4550,19 +4151,16 @@
         <v>0.816987706248283</v>
       </c>
       <c r="H133" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I133" t="s">
-        <v>22</v>
-      </c>
-      <c r="J133" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134">
       <c r="A134"/>
       <c r="B134" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C134" t="n">
         <v>15</v>
@@ -4580,19 +4178,16 @@
         <v>0.878273300965591</v>
       </c>
       <c r="H134" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I134" t="s">
-        <v>14</v>
-      </c>
-      <c r="J134" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135">
       <c r="A135"/>
       <c r="B135" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C135" t="n">
         <v>15</v>
@@ -4610,19 +4205,16 @@
         <v>0.859540943467457</v>
       </c>
       <c r="H135" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I135" t="s">
-        <v>17</v>
-      </c>
-      <c r="J135" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136">
       <c r="A136"/>
       <c r="B136" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C136" t="n">
         <v>15</v>
@@ -4640,19 +4232,16 @@
         <v>0.859540943467457</v>
       </c>
       <c r="H136" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I136" t="s">
-        <v>17</v>
-      </c>
-      <c r="J136" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137">
       <c r="A137"/>
       <c r="B137" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C137" t="n">
         <v>15</v>
@@ -4670,19 +4259,16 @@
         <v>0.733535113911462</v>
       </c>
       <c r="H137" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I137" t="s">
-        <v>17</v>
-      </c>
-      <c r="J137" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138">
       <c r="A138"/>
       <c r="B138" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C138" t="n">
         <v>13</v>
@@ -4700,19 +4286,16 @@
         <v>0.729972569590586</v>
       </c>
       <c r="H138" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I138" t="s">
-        <v>18</v>
-      </c>
-      <c r="J138" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139">
       <c r="A139"/>
       <c r="B139" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C139" t="n">
         <v>14</v>
@@ -4730,19 +4313,16 @@
         <v>0.876650972828681</v>
       </c>
       <c r="H139" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I139" t="s">
-        <v>18</v>
-      </c>
-      <c r="J139" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140">
       <c r="A140"/>
       <c r="B140" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C140" t="n">
         <v>14</v>
@@ -4760,19 +4340,16 @@
         <v>0.62787066705352</v>
       </c>
       <c r="H140" t="s">
+        <v>15</v>
+      </c>
+      <c r="I140" t="s">
         <v>16</v>
-      </c>
-      <c r="I140" t="s">
-        <v>17</v>
-      </c>
-      <c r="J140" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="141">
       <c r="A141"/>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C141" t="n">
         <v>14</v>
@@ -4790,19 +4367,16 @@
         <v>0.62787066705352</v>
       </c>
       <c r="H141" t="s">
+        <v>15</v>
+      </c>
+      <c r="I141" t="s">
         <v>16</v>
-      </c>
-      <c r="I141" t="s">
-        <v>17</v>
-      </c>
-      <c r="J141" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="142">
       <c r="A142"/>
       <c r="B142" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C142" t="n">
         <v>14</v>
@@ -4820,19 +4394,16 @@
         <v>0.750621470228176</v>
       </c>
       <c r="H142" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I142" t="s">
-        <v>22</v>
-      </c>
-      <c r="J142" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143">
       <c r="A143"/>
       <c r="B143" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C143" t="n">
         <v>15</v>
@@ -4850,19 +4421,16 @@
         <v>0.443140934823514</v>
       </c>
       <c r="H143" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I143" t="s">
-        <v>14</v>
-      </c>
-      <c r="J143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144">
       <c r="A144"/>
       <c r="B144" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C144" t="n">
         <v>15</v>
@@ -4880,19 +4448,16 @@
         <v>0.630908856824771</v>
       </c>
       <c r="H144" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I144" t="s">
-        <v>28</v>
-      </c>
-      <c r="J144" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145">
       <c r="A145"/>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C145" t="n">
         <v>15</v>
@@ -4910,19 +4475,16 @@
         <v>0.878273300965591</v>
       </c>
       <c r="H145" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I145" t="s">
-        <v>14</v>
-      </c>
-      <c r="J145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146">
       <c r="A146"/>
       <c r="B146" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C146" t="n">
         <v>14</v>
@@ -4940,19 +4502,16 @@
         <v>0.750621470228176</v>
       </c>
       <c r="H146" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I146" t="s">
-        <v>22</v>
-      </c>
-      <c r="J146" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147"/>
       <c r="B147" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C147" t="n">
         <v>15</v>
@@ -4970,19 +4529,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H147" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I147" t="s">
-        <v>12</v>
-      </c>
-      <c r="J147" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148">
       <c r="A148"/>
       <c r="B148" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C148" t="n">
         <v>15</v>
@@ -5000,19 +4556,16 @@
         <v>0.733535113911462</v>
       </c>
       <c r="H148" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I148" t="s">
-        <v>17</v>
-      </c>
-      <c r="J148" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149">
       <c r="A149"/>
       <c r="B149" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C149" t="n">
         <v>15</v>
@@ -5030,19 +4583,16 @@
         <v>0.823875422930297</v>
       </c>
       <c r="H149" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I149" t="s">
-        <v>12</v>
-      </c>
-      <c r="J149" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="150">
       <c r="A150"/>
       <c r="B150" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C150" t="n">
         <v>14</v>
@@ -5060,19 +4610,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H150" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I150" t="s">
-        <v>22</v>
-      </c>
-      <c r="J150" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151">
       <c r="A151"/>
       <c r="B151" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C151" t="n">
         <v>15</v>
@@ -5090,19 +4637,16 @@
         <v>0.708648073909734</v>
       </c>
       <c r="H151" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I151" t="s">
-        <v>28</v>
-      </c>
-      <c r="J151" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="152">
       <c r="A152"/>
       <c r="B152" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C152" t="n">
         <v>15</v>
@@ -5120,19 +4664,16 @@
         <v>0.859540943467457</v>
       </c>
       <c r="H152" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I152" t="s">
-        <v>17</v>
-      </c>
-      <c r="J152" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153">
       <c r="A153"/>
       <c r="B153" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C153" t="n">
         <v>15</v>
@@ -5150,19 +4691,16 @@
         <v>0.622628985316801</v>
       </c>
       <c r="H153" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I153" t="s">
-        <v>12</v>
-      </c>
-      <c r="J153" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="154">
       <c r="A154"/>
       <c r="B154" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C154" t="n">
         <v>15</v>
@@ -5180,19 +4718,16 @@
         <v>0.979753656625192</v>
       </c>
       <c r="H154" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I154" t="s">
-        <v>14</v>
-      </c>
-      <c r="J154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="155">
       <c r="A155"/>
       <c r="B155" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C155" t="n">
         <v>15</v>
@@ -5210,19 +4745,16 @@
         <v>0.756051387063227</v>
       </c>
       <c r="H155" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I155" t="s">
-        <v>14</v>
-      </c>
-      <c r="J155" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="156">
       <c r="A156"/>
       <c r="B156" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C156" t="n">
         <v>15</v>
@@ -5240,19 +4772,16 @@
         <v>0.733535113911462</v>
       </c>
       <c r="H156" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I156" t="s">
-        <v>17</v>
-      </c>
-      <c r="J156" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157">
       <c r="A157"/>
       <c r="B157" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C157" t="n">
         <v>15</v>
@@ -5270,19 +4799,16 @@
         <v>0.848787679919784</v>
       </c>
       <c r="H157" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I157" t="s">
-        <v>12</v>
-      </c>
-      <c r="J157" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158">
       <c r="A158"/>
       <c r="B158" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C158" t="n">
         <v>13</v>
@@ -5300,19 +4826,16 @@
         <v>0.734159618041601</v>
       </c>
       <c r="H158" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I158" t="s">
-        <v>22</v>
-      </c>
-      <c r="J158" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159">
       <c r="A159"/>
       <c r="B159" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C159" t="n">
         <v>15</v>
@@ -5330,19 +4853,16 @@
         <v>0.443140934823514</v>
       </c>
       <c r="H159" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I159" t="s">
-        <v>14</v>
-      </c>
-      <c r="J159" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160">
       <c r="A160"/>
       <c r="B160" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C160" t="n">
         <v>14</v>
@@ -5360,19 +4880,16 @@
         <v>0.823197435247269</v>
       </c>
       <c r="H160" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I160" t="s">
-        <v>28</v>
-      </c>
-      <c r="J160" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="161">
       <c r="A161"/>
       <c r="B161" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C161" t="n">
         <v>14</v>
@@ -5390,19 +4907,16 @@
         <v>0.816987706248283</v>
       </c>
       <c r="H161" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I161" t="s">
-        <v>22</v>
-      </c>
-      <c r="J161" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="162">
       <c r="A162"/>
       <c r="B162" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C162" t="n">
         <v>14</v>
@@ -5420,19 +4934,16 @@
         <v>0.76627806073437</v>
       </c>
       <c r="H162" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I162" t="s">
-        <v>12</v>
-      </c>
-      <c r="J162" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="163">
       <c r="A163"/>
       <c r="B163" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C163" t="n">
         <v>15</v>
@@ -5450,19 +4961,16 @@
         <v>0.708648073909734</v>
       </c>
       <c r="H163" t="s">
+        <v>10</v>
+      </c>
+      <c r="I163" t="s">
         <v>11</v>
-      </c>
-      <c r="I163" t="s">
-        <v>12</v>
-      </c>
-      <c r="J163" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164"/>
       <c r="B164" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C164" t="n">
         <v>15</v>
@@ -5480,19 +4988,16 @@
         <v>0.708648073909734</v>
       </c>
       <c r="H164" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I164" t="s">
-        <v>28</v>
-      </c>
-      <c r="J164" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="165">
       <c r="A165"/>
       <c r="B165" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C165" t="n">
         <v>15</v>
@@ -5510,19 +5015,16 @@
         <v>0.774291101788778</v>
       </c>
       <c r="H165" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I165" t="s">
-        <v>17</v>
-      </c>
-      <c r="J165" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="166">
       <c r="A166"/>
       <c r="B166" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C166" t="n">
         <v>15</v>
@@ -5540,19 +5042,16 @@
         <v>0.979844227761598</v>
       </c>
       <c r="H166" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I166" t="s">
-        <v>14</v>
-      </c>
-      <c r="J166" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="167">
       <c r="A167"/>
       <c r="B167" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C167" t="n">
         <v>15</v>
@@ -5570,19 +5069,16 @@
         <v>0.622628985316801</v>
       </c>
       <c r="H167" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I167" t="s">
-        <v>12</v>
-      </c>
-      <c r="J167" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="168">
       <c r="A168"/>
       <c r="B168" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C168" t="n">
         <v>14</v>
@@ -5600,19 +5096,16 @@
         <v>0.888598550131416</v>
       </c>
       <c r="H168" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I168" t="s">
-        <v>22</v>
-      </c>
-      <c r="J168" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="169">
       <c r="A169"/>
       <c r="B169" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C169" t="n">
         <v>14</v>
@@ -5630,19 +5123,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H169" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I169" t="s">
-        <v>22</v>
-      </c>
-      <c r="J169" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="170">
       <c r="A170"/>
       <c r="B170" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C170" t="n">
         <v>15</v>
@@ -5660,19 +5150,16 @@
         <v>0.630908856824771</v>
       </c>
       <c r="H170" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I170" t="s">
-        <v>28</v>
-      </c>
-      <c r="J170" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="171">
       <c r="A171"/>
       <c r="B171" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C171" t="n">
         <v>15</v>
@@ -5690,19 +5177,16 @@
         <v>0.807658284963743</v>
       </c>
       <c r="H171" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I171" t="s">
-        <v>28</v>
-      </c>
-      <c r="J171" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="172">
       <c r="A172"/>
       <c r="B172" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C172" t="n">
         <v>15</v>
@@ -5720,19 +5204,16 @@
         <v>0.733535113911462</v>
       </c>
       <c r="H172" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I172" t="s">
-        <v>17</v>
-      </c>
-      <c r="J172" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173">
       <c r="A173"/>
       <c r="B173" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C173" t="n">
         <v>13</v>
@@ -5750,19 +5231,16 @@
         <v>0.73756644882971</v>
       </c>
       <c r="H173" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I173" t="s">
-        <v>18</v>
-      </c>
-      <c r="J173" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="174">
       <c r="A174"/>
       <c r="B174" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C174" t="n">
         <v>15</v>
@@ -5780,19 +5258,16 @@
         <v>0.650644810911348</v>
       </c>
       <c r="H174" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I174" t="s">
-        <v>17</v>
-      </c>
-      <c r="J174" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175">
       <c r="A175"/>
       <c r="B175" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C175" t="n">
         <v>15</v>
@@ -5810,19 +5285,16 @@
         <v>0.774291101788778</v>
       </c>
       <c r="H175" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I175" t="s">
-        <v>17</v>
-      </c>
-      <c r="J175" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="176">
       <c r="A176"/>
       <c r="B176" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C176" t="n">
         <v>15</v>
@@ -5840,19 +5312,16 @@
         <v>0.823875422930297</v>
       </c>
       <c r="H176" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I176" t="s">
-        <v>12</v>
-      </c>
-      <c r="J176" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="177">
       <c r="A177"/>
       <c r="B177" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C177" t="n">
         <v>15</v>
@@ -5870,19 +5339,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H177" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I177" t="s">
-        <v>17</v>
-      </c>
-      <c r="J177" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178">
       <c r="A178"/>
       <c r="B178" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C178" t="n">
         <v>15</v>
@@ -5900,19 +5366,16 @@
         <v>0.823875422930297</v>
       </c>
       <c r="H178" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I178" t="s">
-        <v>12</v>
-      </c>
-      <c r="J178" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179">
       <c r="A179"/>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C179" t="n">
         <v>14</v>
@@ -5930,19 +5393,16 @@
         <v>0.852007703632368</v>
       </c>
       <c r="H179" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I179" t="s">
-        <v>22</v>
-      </c>
-      <c r="J179" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="180">
       <c r="A180"/>
       <c r="B180" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C180" t="n">
         <v>14</v>
@@ -5960,19 +5420,16 @@
         <v>0.823197435247269</v>
       </c>
       <c r="H180" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I180" t="s">
-        <v>28</v>
-      </c>
-      <c r="J180" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="181">
       <c r="A181"/>
       <c r="B181" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C181" t="n">
         <v>14</v>
@@ -5990,19 +5447,16 @@
         <v>0.869333899732566</v>
       </c>
       <c r="H181" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I181" t="s">
-        <v>14</v>
-      </c>
-      <c r="J181" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="182">
       <c r="A182"/>
       <c r="B182" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C182" t="n">
         <v>14</v>
@@ -6020,19 +5474,16 @@
         <v>0.823197435247269</v>
       </c>
       <c r="H182" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I182" t="s">
-        <v>28</v>
-      </c>
-      <c r="J182" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="183">
       <c r="A183"/>
       <c r="B183" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C183" t="n">
         <v>15</v>
@@ -6050,19 +5501,16 @@
         <v>0.756051387063227</v>
       </c>
       <c r="H183" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I183" t="s">
-        <v>14</v>
-      </c>
-      <c r="J183" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="184">
       <c r="A184"/>
       <c r="B184" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C184" t="n">
         <v>13</v>
@@ -6080,19 +5528,16 @@
         <v>0.734159618041601</v>
       </c>
       <c r="H184" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I184" t="s">
-        <v>22</v>
-      </c>
-      <c r="J184" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185">
       <c r="A185"/>
       <c r="B185" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C185" t="n">
         <v>13</v>
@@ -6110,19 +5555,16 @@
         <v>0.734159618041601</v>
       </c>
       <c r="H185" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I185" t="s">
-        <v>22</v>
-      </c>
-      <c r="J185" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="186">
       <c r="A186"/>
       <c r="B186" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C186" t="n">
         <v>15</v>
@@ -6140,19 +5582,16 @@
         <v>0.807658284963743</v>
       </c>
       <c r="H186" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I186" t="s">
-        <v>28</v>
-      </c>
-      <c r="J186" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="187">
       <c r="A187"/>
       <c r="B187" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C187" t="n">
         <v>15</v>
@@ -6170,19 +5609,16 @@
         <v>0.848787679919784</v>
       </c>
       <c r="H187" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I187" t="s">
-        <v>12</v>
-      </c>
-      <c r="J187" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188">
       <c r="A188"/>
       <c r="B188" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C188" t="n">
         <v>15</v>
@@ -6200,19 +5636,16 @@
         <v>0.804050630543897</v>
       </c>
       <c r="H188" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I188" t="s">
-        <v>28</v>
-      </c>
-      <c r="J188" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="189">
       <c r="A189"/>
       <c r="B189" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C189" t="n">
         <v>14</v>
@@ -6230,19 +5663,16 @@
         <v>0.888598550131416</v>
       </c>
       <c r="H189" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I189" t="s">
-        <v>22</v>
-      </c>
-      <c r="J189" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="190">
       <c r="A190"/>
       <c r="B190" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C190" t="n">
         <v>14</v>
@@ -6260,19 +5690,16 @@
         <v>0.875502537632114</v>
       </c>
       <c r="H190" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I190" t="s">
-        <v>18</v>
-      </c>
-      <c r="J190" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="191">
       <c r="A191"/>
       <c r="B191" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C191" t="n">
         <v>15</v>
@@ -6290,19 +5717,16 @@
         <v>0.661554881899552</v>
       </c>
       <c r="H191" t="s">
+        <v>26</v>
+      </c>
+      <c r="I191" t="s">
         <v>27</v>
-      </c>
-      <c r="I191" t="s">
-        <v>28</v>
-      </c>
-      <c r="J191" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="192">
       <c r="A192"/>
       <c r="B192" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C192" t="n">
         <v>15</v>
@@ -6320,19 +5744,16 @@
         <v>0.878273300965591</v>
       </c>
       <c r="H192" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I192" t="s">
-        <v>14</v>
-      </c>
-      <c r="J192" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193">
       <c r="A193"/>
       <c r="B193" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C193" t="n">
         <v>15</v>
@@ -6350,19 +5771,16 @@
         <v>0.823875422930297</v>
       </c>
       <c r="H193" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I193" t="s">
-        <v>12</v>
-      </c>
-      <c r="J193" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="194">
       <c r="A194"/>
       <c r="B194" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C194" t="n">
         <v>14</v>
@@ -6380,19 +5798,16 @@
         <v>0.888598550131416</v>
       </c>
       <c r="H194" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I194" t="s">
-        <v>22</v>
-      </c>
-      <c r="J194" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="195">
       <c r="A195"/>
       <c r="B195" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C195" t="n">
         <v>14</v>
@@ -6410,19 +5825,16 @@
         <v>0.76627806073437</v>
       </c>
       <c r="H195" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I195" t="s">
-        <v>12</v>
-      </c>
-      <c r="J195" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196">
       <c r="A196"/>
       <c r="B196" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C196" t="n">
         <v>14</v>
@@ -6440,19 +5852,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H196" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I196" t="s">
-        <v>18</v>
-      </c>
-      <c r="J196" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="197">
       <c r="A197"/>
       <c r="B197" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C197" t="n">
         <v>14</v>
@@ -6470,19 +5879,16 @@
         <v>0.836799571957948</v>
       </c>
       <c r="H197" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I197" t="s">
-        <v>22</v>
-      </c>
-      <c r="J197" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198">
       <c r="A198"/>
       <c r="B198" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C198" t="n">
         <v>15</v>
@@ -6500,19 +5906,16 @@
         <v>0.804050630543897</v>
       </c>
       <c r="H198" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I198" t="s">
-        <v>28</v>
-      </c>
-      <c r="J198" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="199">
       <c r="A199"/>
       <c r="B199" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C199" t="n">
         <v>13</v>
@@ -6530,19 +5933,16 @@
         <v>0.734159618041601</v>
       </c>
       <c r="H199" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I199" t="s">
-        <v>22</v>
-      </c>
-      <c r="J199" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="200">
       <c r="A200"/>
       <c r="B200" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C200" t="n">
         <v>14</v>
@@ -6560,19 +5960,16 @@
         <v>0.823197435247269</v>
       </c>
       <c r="H200" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I200" t="s">
-        <v>28</v>
-      </c>
-      <c r="J200" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="201">
       <c r="A201"/>
       <c r="B201" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C201" t="n">
         <v>15</v>
@@ -6590,19 +5987,16 @@
         <v>0.804050630543897</v>
       </c>
       <c r="H201" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I201" t="s">
-        <v>28</v>
-      </c>
-      <c r="J201" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="202">
       <c r="A202"/>
       <c r="B202" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C202" t="n">
         <v>15</v>
@@ -6620,19 +6014,16 @@
         <v>0.661554881899552</v>
       </c>
       <c r="H202" t="s">
+        <v>26</v>
+      </c>
+      <c r="I202" t="s">
         <v>27</v>
-      </c>
-      <c r="I202" t="s">
-        <v>28</v>
-      </c>
-      <c r="J202" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="203">
       <c r="A203"/>
       <c r="B203" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C203" t="n">
         <v>15</v>
@@ -6650,19 +6041,16 @@
         <v>0.859540943467457</v>
       </c>
       <c r="H203" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I203" t="s">
-        <v>17</v>
-      </c>
-      <c r="J203" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="204">
       <c r="A204"/>
       <c r="B204" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C204" t="n">
         <v>14</v>
@@ -6680,19 +6068,16 @@
         <v>0.869333899732566</v>
       </c>
       <c r="H204" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I204" t="s">
-        <v>14</v>
-      </c>
-      <c r="J204" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="205">
       <c r="A205"/>
       <c r="B205" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C205" t="n">
         <v>15</v>
@@ -6710,19 +6095,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H205" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I205" t="s">
-        <v>12</v>
-      </c>
-      <c r="J205" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="206">
       <c r="A206"/>
       <c r="B206" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C206" t="n">
         <v>15</v>
@@ -6740,19 +6122,16 @@
         <v>0.756051387063227</v>
       </c>
       <c r="H206" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I206" t="s">
-        <v>14</v>
-      </c>
-      <c r="J206" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="207">
       <c r="A207"/>
       <c r="B207" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C207" t="n">
         <v>15</v>
@@ -6770,19 +6149,16 @@
         <v>0.774291101788778</v>
       </c>
       <c r="H207" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I207" t="s">
-        <v>17</v>
-      </c>
-      <c r="J207" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="208">
       <c r="A208"/>
       <c r="B208" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C208" t="n">
         <v>14</v>
@@ -6800,19 +6176,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H208" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I208" t="s">
-        <v>18</v>
-      </c>
-      <c r="J208" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="209">
       <c r="A209"/>
       <c r="B209" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C209" t="n">
         <v>15</v>
@@ -6830,19 +6203,16 @@
         <v>0.848787679919784</v>
       </c>
       <c r="H209" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I209" t="s">
-        <v>12</v>
-      </c>
-      <c r="J209" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="210">
       <c r="A210"/>
       <c r="B210" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C210" t="n">
         <v>15</v>
@@ -6860,19 +6230,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H210" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I210" t="s">
-        <v>12</v>
-      </c>
-      <c r="J210" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="211">
       <c r="A211"/>
       <c r="B211" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C211" t="n">
         <v>14</v>
@@ -6890,19 +6257,16 @@
         <v>0.76627806073437</v>
       </c>
       <c r="H211" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I211" t="s">
-        <v>12</v>
-      </c>
-      <c r="J211" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="212">
       <c r="A212"/>
       <c r="B212" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C212" t="n">
         <v>14</v>
@@ -6920,19 +6284,16 @@
         <v>0.852007703632368</v>
       </c>
       <c r="H212" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I212" t="s">
-        <v>22</v>
-      </c>
-      <c r="J212" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="213">
       <c r="A213"/>
       <c r="B213" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C213" t="n">
         <v>14</v>
@@ -6950,19 +6311,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H213" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I213" t="s">
-        <v>18</v>
-      </c>
-      <c r="J213" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="214">
       <c r="A214"/>
       <c r="B214" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C214" t="n">
         <v>14</v>
@@ -6980,19 +6338,16 @@
         <v>0.888598550131416</v>
       </c>
       <c r="H214" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I214" t="s">
-        <v>22</v>
-      </c>
-      <c r="J214" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="215">
       <c r="A215"/>
       <c r="B215" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C215" t="n">
         <v>14</v>
@@ -7010,19 +6365,16 @@
         <v>0.869333899732566</v>
       </c>
       <c r="H215" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I215" t="s">
-        <v>14</v>
-      </c>
-      <c r="J215" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="216">
       <c r="A216"/>
       <c r="B216" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C216" t="n">
         <v>15</v>
@@ -7040,19 +6392,16 @@
         <v>0.979844227761598</v>
       </c>
       <c r="H216" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I216" t="s">
-        <v>14</v>
-      </c>
-      <c r="J216" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="217">
       <c r="A217"/>
       <c r="B217" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C217" t="n">
         <v>15</v>
@@ -7070,19 +6419,16 @@
         <v>0.804050630543897</v>
       </c>
       <c r="H217" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I217" t="s">
-        <v>28</v>
-      </c>
-      <c r="J217" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="218">
       <c r="A218"/>
       <c r="B218" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C218" t="n">
         <v>15</v>
@@ -7100,19 +6446,16 @@
         <v>0.859540943467457</v>
       </c>
       <c r="H218" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I218" t="s">
-        <v>17</v>
-      </c>
-      <c r="J218" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="219">
       <c r="A219"/>
       <c r="B219" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C219" t="n">
         <v>15</v>
@@ -7130,19 +6473,16 @@
         <v>0.791934825830218</v>
       </c>
       <c r="H219" t="s">
+        <v>10</v>
+      </c>
+      <c r="I219" t="s">
         <v>11</v>
-      </c>
-      <c r="I219" t="s">
-        <v>12</v>
-      </c>
-      <c r="J219" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="220">
       <c r="A220"/>
       <c r="B220" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C220" t="n">
         <v>14</v>
@@ -7160,19 +6500,16 @@
         <v>0.76627806073437</v>
       </c>
       <c r="H220" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I220" t="s">
-        <v>12</v>
-      </c>
-      <c r="J220" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="221">
       <c r="A221"/>
       <c r="B221" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C221" t="n">
         <v>14</v>
@@ -7190,19 +6527,16 @@
         <v>0.869333899732566</v>
       </c>
       <c r="H221" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I221" t="s">
-        <v>14</v>
-      </c>
-      <c r="J221" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="222">
       <c r="A222"/>
       <c r="B222" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C222" t="n">
         <v>14</v>
@@ -7220,19 +6554,16 @@
         <v>0.852007703632368</v>
       </c>
       <c r="H222" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I222" t="s">
-        <v>22</v>
-      </c>
-      <c r="J222" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="223">
       <c r="A223"/>
       <c r="B223" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C223" t="n">
         <v>14</v>
@@ -7250,19 +6581,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H223" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I223" t="s">
-        <v>18</v>
-      </c>
-      <c r="J223" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="224">
       <c r="A224"/>
       <c r="B224" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C224" t="n">
         <v>15</v>
@@ -7280,19 +6608,16 @@
         <v>0.878273300965591</v>
       </c>
       <c r="H224" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I224" t="s">
-        <v>14</v>
-      </c>
-      <c r="J224" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="225">
       <c r="A225"/>
       <c r="B225" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C225" t="n">
         <v>15</v>
@@ -7310,19 +6635,16 @@
         <v>0.804050630543897</v>
       </c>
       <c r="H225" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I225" t="s">
-        <v>28</v>
-      </c>
-      <c r="J225" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="226">
       <c r="A226"/>
       <c r="B226" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C226" t="n">
         <v>14</v>
@@ -7340,19 +6662,16 @@
         <v>0.764314765137152</v>
       </c>
       <c r="H226" t="s">
+        <v>15</v>
+      </c>
+      <c r="I226" t="s">
         <v>16</v>
-      </c>
-      <c r="I226" t="s">
-        <v>17</v>
-      </c>
-      <c r="J226" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="227">
       <c r="A227"/>
       <c r="B227" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C227" t="n">
         <v>15</v>
@@ -7370,19 +6689,16 @@
         <v>0.774291101788778</v>
       </c>
       <c r="H227" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I227" t="s">
-        <v>17</v>
-      </c>
-      <c r="J227" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="228">
       <c r="A228"/>
       <c r="B228" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C228" t="n">
         <v>14</v>
@@ -7400,19 +6716,16 @@
         <v>0.852007703632368</v>
       </c>
       <c r="H228" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I228" t="s">
-        <v>22</v>
-      </c>
-      <c r="J228" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="229">
       <c r="A229"/>
       <c r="B229" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C229" t="n">
         <v>14</v>
@@ -7430,19 +6743,16 @@
         <v>0.823197435247269</v>
       </c>
       <c r="H229" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I229" t="s">
-        <v>28</v>
-      </c>
-      <c r="J229" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="230">
       <c r="A230"/>
       <c r="B230" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C230" t="n">
         <v>15</v>
@@ -7460,19 +6770,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H230" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I230" t="s">
-        <v>17</v>
-      </c>
-      <c r="J230" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="231">
       <c r="A231"/>
       <c r="B231" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C231" t="n">
         <v>15</v>
@@ -7490,19 +6797,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H231" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I231" t="s">
-        <v>17</v>
-      </c>
-      <c r="J231" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="232">
       <c r="A232"/>
       <c r="B232" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C232" t="n">
         <v>14</v>
@@ -7520,19 +6824,16 @@
         <v>0.890614350979531</v>
       </c>
       <c r="H232" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I232" t="s">
-        <v>22</v>
-      </c>
-      <c r="J232" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="233">
       <c r="A233"/>
       <c r="B233" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C233" t="n">
         <v>15</v>
@@ -7550,19 +6851,16 @@
         <v>0.979753656625192</v>
       </c>
       <c r="H233" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I233" t="s">
-        <v>14</v>
-      </c>
-      <c r="J233" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="234">
       <c r="A234"/>
       <c r="B234" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C234" t="n">
         <v>15</v>
@@ -7580,19 +6878,16 @@
         <v>0.75844521821188</v>
       </c>
       <c r="H234" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I234" t="s">
-        <v>14</v>
-      </c>
-      <c r="J234" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="235">
       <c r="A235"/>
       <c r="B235" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C235" t="n">
         <v>15</v>
@@ -7610,19 +6905,16 @@
         <v>0.848787679919784</v>
       </c>
       <c r="H235" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I235" t="s">
-        <v>12</v>
-      </c>
-      <c r="J235" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="236">
       <c r="A236"/>
       <c r="B236" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C236" t="n">
         <v>14</v>
@@ -7640,19 +6932,16 @@
         <v>0.888598550131416</v>
       </c>
       <c r="H236" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I236" t="s">
-        <v>18</v>
-      </c>
-      <c r="J236" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="237">
       <c r="A237"/>
       <c r="B237" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C237" t="n">
         <v>14</v>
@@ -7670,19 +6959,16 @@
         <v>0.764314765137152</v>
       </c>
       <c r="H237" t="s">
+        <v>15</v>
+      </c>
+      <c r="I237" t="s">
         <v>16</v>
-      </c>
-      <c r="I237" t="s">
-        <v>17</v>
-      </c>
-      <c r="J237" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="238">
       <c r="A238"/>
       <c r="B238" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C238" t="n">
         <v>14</v>
@@ -7700,19 +6986,16 @@
         <v>0.888598550131416</v>
       </c>
       <c r="H238" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I238" t="s">
-        <v>18</v>
-      </c>
-      <c r="J238" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="239">
       <c r="A239"/>
       <c r="B239" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C239" t="n">
         <v>15</v>
@@ -7730,19 +7013,16 @@
         <v>0.741147994563553</v>
       </c>
       <c r="H239" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I239" t="s">
-        <v>17</v>
-      </c>
-      <c r="J239" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="240">
       <c r="A240"/>
       <c r="B240" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C240" t="n">
         <v>15</v>
@@ -7760,19 +7040,16 @@
         <v>0.878273300965591</v>
       </c>
       <c r="H240" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I240" t="s">
-        <v>17</v>
-      </c>
-      <c r="J240" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="241">
       <c r="A241"/>
       <c r="B241" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C241" t="n">
         <v>15</v>
@@ -7790,19 +7067,16 @@
         <v>0.878273300965591</v>
       </c>
       <c r="H241" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I241" t="s">
-        <v>14</v>
-      </c>
-      <c r="J241" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="242">
       <c r="A242"/>
       <c r="B242" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C242" t="n">
         <v>14</v>
@@ -7820,19 +7094,16 @@
         <v>0.76627806073437</v>
       </c>
       <c r="H242" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I242" t="s">
-        <v>12</v>
-      </c>
-      <c r="J242" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="243">
       <c r="A243"/>
       <c r="B243" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C243" t="n">
         <v>14</v>
@@ -7850,19 +7121,16 @@
         <v>0.888598550131416</v>
       </c>
       <c r="H243" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I243" t="s">
-        <v>18</v>
-      </c>
-      <c r="J243" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="244">
       <c r="A244"/>
       <c r="B244" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C244" t="n">
         <v>14</v>
@@ -7880,19 +7148,16 @@
         <v>0.888598550131416</v>
       </c>
       <c r="H244" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I244" t="s">
-        <v>22</v>
-      </c>
-      <c r="J244" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="245">
       <c r="A245"/>
       <c r="B245" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C245" t="n">
         <v>14</v>
@@ -7910,19 +7175,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H245" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I245" t="s">
-        <v>18</v>
-      </c>
-      <c r="J245" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="246">
       <c r="A246"/>
       <c r="B246" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C246" t="n">
         <v>14</v>
@@ -7940,19 +7202,16 @@
         <v>0.890614350979531</v>
       </c>
       <c r="H246" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I246" t="s">
-        <v>22</v>
-      </c>
-      <c r="J246" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="247">
       <c r="A247"/>
       <c r="B247" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C247" t="n">
         <v>14</v>
@@ -7970,19 +7229,16 @@
         <v>0.845400416951637</v>
       </c>
       <c r="H247" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I247" t="s">
-        <v>22</v>
-      </c>
-      <c r="J247" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="248">
       <c r="A248"/>
       <c r="B248" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C248" t="n">
         <v>15</v>
@@ -8000,19 +7256,16 @@
         <v>0.859540943467457</v>
       </c>
       <c r="H248" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I248" t="s">
-        <v>17</v>
-      </c>
-      <c r="J248" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="249">
       <c r="A249"/>
       <c r="B249" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C249" t="n">
         <v>14</v>
@@ -8030,19 +7283,16 @@
         <v>0.869333899732566</v>
       </c>
       <c r="H249" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I249" t="s">
-        <v>14</v>
-      </c>
-      <c r="J249" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="250">
       <c r="A250"/>
       <c r="B250" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C250" t="n">
         <v>15</v>
@@ -8060,19 +7310,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H250" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I250" t="s">
-        <v>12</v>
-      </c>
-      <c r="J250" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="251">
       <c r="A251"/>
       <c r="B251" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C251" t="n">
         <v>15</v>
@@ -8090,19 +7337,16 @@
         <v>0.79518705780703</v>
       </c>
       <c r="H251" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I251" t="s">
-        <v>28</v>
-      </c>
-      <c r="J251" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="252">
       <c r="A252"/>
       <c r="B252" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C252" t="n">
         <v>15</v>
@@ -8120,19 +7364,16 @@
         <v>0.848787679919784</v>
       </c>
       <c r="H252" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I252" t="s">
-        <v>12</v>
-      </c>
-      <c r="J252" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="253">
       <c r="A253"/>
       <c r="B253" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C253" t="n">
         <v>14</v>
@@ -8150,19 +7391,16 @@
         <v>0.875502537632114</v>
       </c>
       <c r="H253" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I253" t="s">
-        <v>18</v>
-      </c>
-      <c r="J253" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="254">
       <c r="A254"/>
       <c r="B254" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C254" t="n">
         <v>15</v>
@@ -8180,19 +7418,16 @@
         <v>0.848787679919784</v>
       </c>
       <c r="H254" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I254" t="s">
-        <v>12</v>
-      </c>
-      <c r="J254" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="255">
       <c r="A255"/>
       <c r="B255" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C255" t="n">
         <v>14</v>
@@ -8210,19 +7445,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H255" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I255" t="s">
-        <v>22</v>
-      </c>
-      <c r="J255" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="256">
       <c r="A256"/>
       <c r="B256" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C256" t="n">
         <v>14</v>
@@ -8240,19 +7472,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H256" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I256" t="s">
-        <v>22</v>
-      </c>
-      <c r="J256" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="257">
       <c r="A257"/>
       <c r="B257" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C257" t="n">
         <v>15</v>
@@ -8270,19 +7499,16 @@
         <v>0.81846046158219</v>
       </c>
       <c r="H257" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I257" t="s">
-        <v>12</v>
-      </c>
-      <c r="J257" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="258">
       <c r="A258"/>
       <c r="B258" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C258" t="n">
         <v>15</v>
@@ -8300,19 +7526,16 @@
         <v>0.876229265560489</v>
       </c>
       <c r="H258" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I258" t="s">
-        <v>28</v>
-      </c>
-      <c r="J258" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="259">
       <c r="A259"/>
       <c r="B259" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C259" t="n">
         <v>15</v>
@@ -8330,19 +7553,16 @@
         <v>0.774291101788778</v>
       </c>
       <c r="H259" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I259" t="s">
-        <v>17</v>
-      </c>
-      <c r="J259" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="260">
       <c r="A260"/>
       <c r="B260" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C260" t="n">
         <v>15</v>
@@ -8360,19 +7580,16 @@
         <v>0.941965423653234</v>
       </c>
       <c r="H260" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I260" t="s">
-        <v>12</v>
-      </c>
-      <c r="J260" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="261">
       <c r="A261"/>
       <c r="B261" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C261" t="n">
         <v>15</v>
@@ -8390,19 +7607,16 @@
         <v>0.979844227761598</v>
       </c>
       <c r="H261" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I261" t="s">
-        <v>14</v>
-      </c>
-      <c r="J261" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="262">
       <c r="A262"/>
       <c r="B262" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C262" t="n">
         <v>14</v>
@@ -8420,19 +7634,16 @@
         <v>0.76627806073437</v>
       </c>
       <c r="H262" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I262" t="s">
-        <v>12</v>
-      </c>
-      <c r="J262" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="263">
       <c r="A263"/>
       <c r="B263" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C263" t="n">
         <v>14</v>
@@ -8450,19 +7661,16 @@
         <v>0.869333899732566</v>
       </c>
       <c r="H263" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I263" t="s">
-        <v>14</v>
-      </c>
-      <c r="J263" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="264">
       <c r="A264"/>
       <c r="B264" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C264" t="n">
         <v>14</v>
@@ -8480,19 +7688,16 @@
         <v>0.845400416951637</v>
       </c>
       <c r="H264" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I264" t="s">
-        <v>22</v>
-      </c>
-      <c r="J264" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="265">
       <c r="A265"/>
       <c r="B265" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C265" t="n">
         <v>14</v>
@@ -8510,19 +7715,16 @@
         <v>0.875502537632114</v>
       </c>
       <c r="H265" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I265" t="s">
-        <v>18</v>
-      </c>
-      <c r="J265" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="266">
       <c r="A266"/>
       <c r="B266" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C266" t="n">
         <v>14</v>
@@ -8540,19 +7742,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H266" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I266" t="s">
-        <v>18</v>
-      </c>
-      <c r="J266" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="267">
       <c r="A267"/>
       <c r="B267" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C267" t="n">
         <v>14</v>
@@ -8570,19 +7769,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H267" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I267" t="s">
-        <v>18</v>
-      </c>
-      <c r="J267" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="268">
       <c r="A268"/>
       <c r="B268" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C268" t="n">
         <v>14</v>
@@ -8600,19 +7796,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H268" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I268" t="s">
-        <v>18</v>
-      </c>
-      <c r="J268" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="269">
       <c r="A269"/>
       <c r="B269" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C269" t="n">
         <v>15</v>
@@ -8630,19 +7823,16 @@
         <v>0.741147994563553</v>
       </c>
       <c r="H269" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I269" t="s">
-        <v>17</v>
-      </c>
-      <c r="J269" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="270">
       <c r="A270"/>
       <c r="B270" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C270" t="n">
         <v>15</v>
@@ -8660,19 +7850,16 @@
         <v>0.848787679919784</v>
       </c>
       <c r="H270" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I270" t="s">
-        <v>12</v>
-      </c>
-      <c r="J270" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="271">
       <c r="A271"/>
       <c r="B271" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C271" t="n">
         <v>15</v>
@@ -8690,19 +7877,16 @@
         <v>0.763908911927806</v>
       </c>
       <c r="H271" t="s">
+        <v>26</v>
+      </c>
+      <c r="I271" t="s">
         <v>27</v>
-      </c>
-      <c r="I271" t="s">
-        <v>28</v>
-      </c>
-      <c r="J271" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="272">
       <c r="A272"/>
       <c r="B272" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C272" t="n">
         <v>15</v>
@@ -8720,19 +7904,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H272" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I272" t="s">
-        <v>12</v>
-      </c>
-      <c r="J272" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="273">
       <c r="A273"/>
       <c r="B273" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C273" t="n">
         <v>14</v>
@@ -8750,19 +7931,16 @@
         <v>0.869333899732566</v>
       </c>
       <c r="H273" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I273" t="s">
-        <v>14</v>
-      </c>
-      <c r="J273" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="274">
       <c r="A274"/>
       <c r="B274" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C274" t="n">
         <v>14</v>
@@ -8780,19 +7958,16 @@
         <v>0.76627806073437</v>
       </c>
       <c r="H274" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I274" t="s">
-        <v>12</v>
-      </c>
-      <c r="J274" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="275">
       <c r="A275"/>
       <c r="B275" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C275" t="n">
         <v>15</v>
@@ -8810,19 +7985,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H275" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I275" t="s">
-        <v>17</v>
-      </c>
-      <c r="J275" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="276">
       <c r="A276"/>
       <c r="B276" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C276" t="n">
         <v>15</v>
@@ -8840,19 +8012,16 @@
         <v>0.774291101788778</v>
       </c>
       <c r="H276" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I276" t="s">
-        <v>17</v>
-      </c>
-      <c r="J276" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="277">
       <c r="A277"/>
       <c r="B277" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C277" t="n">
         <v>15</v>
@@ -8870,19 +8039,16 @@
         <v>0.860323446431975</v>
       </c>
       <c r="H277" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I277" t="s">
-        <v>28</v>
-      </c>
-      <c r="J277" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="278">
       <c r="A278"/>
       <c r="B278" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C278" t="n">
         <v>15</v>
@@ -8900,19 +8066,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H278" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I278" t="s">
-        <v>17</v>
-      </c>
-      <c r="J278" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="279">
       <c r="A279"/>
       <c r="B279" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C279" t="n">
         <v>15</v>
@@ -8930,19 +8093,16 @@
         <v>0.79518705780703</v>
       </c>
       <c r="H279" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I279" t="s">
-        <v>28</v>
-      </c>
-      <c r="J279" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="280">
       <c r="A280"/>
       <c r="B280" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C280" t="n">
         <v>15</v>
@@ -8960,19 +8120,16 @@
         <v>0.859540943467457</v>
       </c>
       <c r="H280" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I280" t="s">
-        <v>17</v>
-      </c>
-      <c r="J280" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="281">
       <c r="A281"/>
       <c r="B281" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C281" t="n">
         <v>15</v>
@@ -8990,19 +8147,16 @@
         <v>0.979753656625192</v>
       </c>
       <c r="H281" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I281" t="s">
-        <v>14</v>
-      </c>
-      <c r="J281" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="282">
       <c r="A282"/>
       <c r="B282" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C282" t="n">
         <v>15</v>
@@ -9020,19 +8174,16 @@
         <v>0.876229265560489</v>
       </c>
       <c r="H282" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I282" t="s">
-        <v>28</v>
-      </c>
-      <c r="J282" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="283">
       <c r="A283"/>
       <c r="B283" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C283" t="n">
         <v>15</v>
@@ -9050,19 +8201,16 @@
         <v>0.979753656625192</v>
       </c>
       <c r="H283" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I283" t="s">
-        <v>14</v>
-      </c>
-      <c r="J283" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="284">
       <c r="A284"/>
       <c r="B284" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C284" t="n">
         <v>15</v>
@@ -9080,19 +8228,16 @@
         <v>0.79518705780703</v>
       </c>
       <c r="H284" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I284" t="s">
-        <v>28</v>
-      </c>
-      <c r="J284" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="285">
       <c r="A285"/>
       <c r="B285" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C285" t="n">
         <v>14</v>
@@ -9110,19 +8255,16 @@
         <v>0.875502537632114</v>
       </c>
       <c r="H285" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I285" t="s">
-        <v>18</v>
-      </c>
-      <c r="J285" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="286">
       <c r="A286"/>
       <c r="B286" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C286" t="n">
         <v>15</v>
@@ -9140,19 +8282,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H286" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I286" t="s">
-        <v>12</v>
-      </c>
-      <c r="J286" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="287">
       <c r="A287"/>
       <c r="B287" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C287" t="n">
         <v>14</v>
@@ -9170,19 +8309,16 @@
         <v>0.869333899732566</v>
       </c>
       <c r="H287" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I287" t="s">
-        <v>14</v>
-      </c>
-      <c r="J287" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="288">
       <c r="A288"/>
       <c r="B288" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C288" t="n">
         <v>15</v>
@@ -9200,19 +8336,16 @@
         <v>0.741147994563553</v>
       </c>
       <c r="H288" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I288" t="s">
-        <v>17</v>
-      </c>
-      <c r="J288" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="289">
       <c r="A289"/>
       <c r="B289" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C289" t="n">
         <v>15</v>
@@ -9230,19 +8363,16 @@
         <v>0.906943900997893</v>
       </c>
       <c r="H289" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I289" t="s">
-        <v>17</v>
-      </c>
-      <c r="J289" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="290">
       <c r="A290"/>
       <c r="B290" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C290" t="n">
         <v>15</v>
@@ -9260,19 +8390,16 @@
         <v>0.979753656625192</v>
       </c>
       <c r="H290" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I290" t="s">
-        <v>14</v>
-      </c>
-      <c r="J290" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="291">
       <c r="A291"/>
       <c r="B291" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C291" t="n">
         <v>14</v>
@@ -9290,19 +8417,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H291" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I291" t="s">
-        <v>18</v>
-      </c>
-      <c r="J291" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="292">
       <c r="A292"/>
       <c r="B292" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C292" t="n">
         <v>14</v>
@@ -9320,19 +8444,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H292" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I292" t="s">
-        <v>18</v>
-      </c>
-      <c r="J292" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="293">
       <c r="A293"/>
       <c r="B293" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C293" t="n">
         <v>14</v>
@@ -9350,19 +8471,16 @@
         <v>0.852007703632368</v>
       </c>
       <c r="H293" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I293" t="s">
-        <v>22</v>
-      </c>
-      <c r="J293" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="294">
       <c r="A294"/>
       <c r="B294" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C294" t="n">
         <v>13</v>
@@ -9380,19 +8498,16 @@
         <v>0.920781456905966</v>
       </c>
       <c r="H294" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I294" t="s">
-        <v>18</v>
-      </c>
-      <c r="J294" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="295">
       <c r="A295"/>
       <c r="B295" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C295" t="n">
         <v>15</v>
@@ -9410,19 +8525,16 @@
         <v>0.979753656625192</v>
       </c>
       <c r="H295" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I295" t="s">
-        <v>14</v>
-      </c>
-      <c r="J295" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="296">
       <c r="A296"/>
       <c r="B296" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C296" t="n">
         <v>15</v>
@@ -9440,19 +8552,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H296" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I296" t="s">
-        <v>12</v>
-      </c>
-      <c r="J296" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="297">
       <c r="A297"/>
       <c r="B297" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C297" t="n">
         <v>15</v>
@@ -9470,19 +8579,16 @@
         <v>0.780754552309047</v>
       </c>
       <c r="H297" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I297" t="s">
-        <v>17</v>
-      </c>
-      <c r="J297" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="298">
       <c r="A298"/>
       <c r="B298" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C298" t="n">
         <v>14</v>
@@ -9500,19 +8606,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H298" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I298" t="s">
-        <v>18</v>
-      </c>
-      <c r="J298" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="299">
       <c r="A299"/>
       <c r="B299" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C299" t="n">
         <v>15</v>
@@ -9530,19 +8633,16 @@
         <v>0.934570930455368</v>
       </c>
       <c r="H299" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I299" t="s">
-        <v>28</v>
-      </c>
-      <c r="J299" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="300">
       <c r="A300"/>
       <c r="B300" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C300" t="n">
         <v>15</v>
@@ -9560,19 +8660,16 @@
         <v>0.966179859523105</v>
       </c>
       <c r="H300" t="s">
+        <v>10</v>
+      </c>
+      <c r="I300" t="s">
         <v>11</v>
-      </c>
-      <c r="I300" t="s">
-        <v>12</v>
-      </c>
-      <c r="J300" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="301">
       <c r="A301"/>
       <c r="B301" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C301" t="n">
         <v>15</v>
@@ -9590,19 +8687,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H301" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I301" t="s">
-        <v>17</v>
-      </c>
-      <c r="J301" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="302">
       <c r="A302"/>
       <c r="B302" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C302" t="n">
         <v>14</v>
@@ -9620,19 +8714,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H302" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I302" t="s">
-        <v>18</v>
-      </c>
-      <c r="J302" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="303">
       <c r="A303"/>
       <c r="B303" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C303" t="n">
         <v>14</v>
@@ -9650,19 +8741,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H303" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I303" t="s">
-        <v>22</v>
-      </c>
-      <c r="J303" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="304">
       <c r="A304"/>
       <c r="B304" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C304" t="n">
         <v>14</v>
@@ -9680,19 +8768,16 @@
         <v>0.879067876743529</v>
       </c>
       <c r="H304" t="s">
+        <v>15</v>
+      </c>
+      <c r="I304" t="s">
         <v>16</v>
-      </c>
-      <c r="I304" t="s">
-        <v>17</v>
-      </c>
-      <c r="J304" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="305">
       <c r="A305"/>
       <c r="B305" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C305" t="n">
         <v>14</v>
@@ -9710,19 +8795,16 @@
         <v>0.976742085270587</v>
       </c>
       <c r="H305" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I305" t="s">
-        <v>28</v>
-      </c>
-      <c r="J305" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="306">
       <c r="A306"/>
       <c r="B306" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C306" t="n">
         <v>15</v>
@@ -9740,19 +8822,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H306" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I306" t="s">
-        <v>14</v>
-      </c>
-      <c r="J306" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="307">
       <c r="A307"/>
       <c r="B307" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C307" t="n">
         <v>15</v>
@@ -9770,19 +8849,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H307" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I307" t="s">
-        <v>12</v>
-      </c>
-      <c r="J307" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="308">
       <c r="A308"/>
       <c r="B308" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C308" t="n">
         <v>15</v>
@@ -9800,19 +8876,16 @@
         <v>0.859540943467457</v>
       </c>
       <c r="H308" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I308" t="s">
-        <v>17</v>
-      </c>
-      <c r="J308" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="309">
       <c r="A309"/>
       <c r="B309" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C309" t="n">
         <v>15</v>
@@ -9830,19 +8903,16 @@
         <v>0.979844227761598</v>
       </c>
       <c r="H309" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I309" t="s">
-        <v>14</v>
-      </c>
-      <c r="J309" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="310">
       <c r="A310"/>
       <c r="B310" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C310" t="n">
         <v>14</v>
@@ -9860,19 +8930,16 @@
         <v>0.852007703632368</v>
       </c>
       <c r="H310" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I310" t="s">
-        <v>22</v>
-      </c>
-      <c r="J310" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="311">
       <c r="A311"/>
       <c r="B311" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C311" t="n">
         <v>14</v>
@@ -9890,19 +8957,16 @@
         <v>0.875502537632114</v>
       </c>
       <c r="H311" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I311" t="s">
-        <v>18</v>
-      </c>
-      <c r="J311" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="312">
       <c r="A312"/>
       <c r="B312" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C312" t="n">
         <v>14</v>
@@ -9920,19 +8984,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H312" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I312" t="s">
-        <v>18</v>
-      </c>
-      <c r="J312" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="313">
       <c r="A313"/>
       <c r="B313" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C313" t="n">
         <v>13</v>
@@ -9950,19 +9011,16 @@
         <v>0.920781456905966</v>
       </c>
       <c r="H313" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I313" t="s">
-        <v>18</v>
-      </c>
-      <c r="J313" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="314">
       <c r="A314"/>
       <c r="B314" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C314" t="n">
         <v>15</v>
@@ -9980,19 +9038,16 @@
         <v>0.901942761851601</v>
       </c>
       <c r="H314" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I314" t="s">
-        <v>14</v>
-      </c>
-      <c r="J314" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="315">
       <c r="A315"/>
       <c r="B315" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C315" t="n">
         <v>14</v>
@@ -10010,19 +9065,16 @@
         <v>0.852007703632368</v>
       </c>
       <c r="H315" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I315" t="s">
-        <v>22</v>
-      </c>
-      <c r="J315" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="316">
       <c r="A316"/>
       <c r="B316" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C316" t="n">
         <v>15</v>
@@ -10040,19 +9092,16 @@
         <v>0.901942761851601</v>
       </c>
       <c r="H316" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I316" t="s">
-        <v>14</v>
-      </c>
-      <c r="J316" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="317">
       <c r="A317"/>
       <c r="B317" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C317" t="n">
         <v>14</v>
@@ -10070,19 +9119,16 @@
         <v>0.822415840592361</v>
       </c>
       <c r="H317" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I317" t="s">
-        <v>12</v>
-      </c>
-      <c r="J317" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="318">
       <c r="A318"/>
       <c r="B318" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C318" t="n">
         <v>14</v>
@@ -10100,19 +9146,16 @@
         <v>0.869333899732566</v>
       </c>
       <c r="H318" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I318" t="s">
-        <v>14</v>
-      </c>
-      <c r="J318" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="319">
       <c r="A319"/>
       <c r="B319" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C319" t="n">
         <v>14</v>
@@ -10130,19 +9173,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H319" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I319" t="s">
-        <v>22</v>
-      </c>
-      <c r="J319" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="320">
       <c r="A320"/>
       <c r="B320" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C320" t="n">
         <v>14</v>
@@ -10160,19 +9200,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H320" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I320" t="s">
-        <v>18</v>
-      </c>
-      <c r="J320" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="321">
       <c r="A321"/>
       <c r="B321" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C321" t="n">
         <v>14</v>
@@ -10190,19 +9227,16 @@
         <v>0.875502537632114</v>
       </c>
       <c r="H321" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I321" t="s">
-        <v>18</v>
-      </c>
-      <c r="J321" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="322">
       <c r="A322"/>
       <c r="B322" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C322" t="n">
         <v>13</v>
@@ -10220,19 +9254,16 @@
         <v>0.920781456905966</v>
       </c>
       <c r="H322" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I322" t="s">
-        <v>18</v>
-      </c>
-      <c r="J322" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="323">
       <c r="A323"/>
       <c r="B323" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C323" t="n">
         <v>15</v>
@@ -10250,19 +9281,16 @@
         <v>0.922886881597157</v>
       </c>
       <c r="H323" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I323" t="s">
-        <v>28</v>
-      </c>
-      <c r="J323" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="324">
       <c r="A324"/>
       <c r="B324" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C324" t="n">
         <v>14</v>
@@ -10280,19 +9308,16 @@
         <v>0.852007703632368</v>
       </c>
       <c r="H324" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I324" t="s">
-        <v>22</v>
-      </c>
-      <c r="J324" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="325">
       <c r="A325"/>
       <c r="B325" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C325" t="n">
         <v>14</v>
@@ -10310,19 +9335,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H325" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I325" t="s">
-        <v>18</v>
-      </c>
-      <c r="J325" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="326">
       <c r="A326"/>
       <c r="B326" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C326" t="n">
         <v>15</v>
@@ -10340,19 +9362,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H326" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I326" t="s">
-        <v>12</v>
-      </c>
-      <c r="J326" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="327">
       <c r="A327"/>
       <c r="B327" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C327" t="n">
         <v>15</v>
@@ -10370,19 +9389,16 @@
         <v>0.934570930455368</v>
       </c>
       <c r="H327" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I327" t="s">
-        <v>28</v>
-      </c>
-      <c r="J327" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="328">
       <c r="A328"/>
       <c r="B328" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C328" t="n">
         <v>13</v>
@@ -10400,19 +9416,16 @@
         <v>0.964377780387274</v>
       </c>
       <c r="H328" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I328" t="s">
-        <v>22</v>
-      </c>
-      <c r="J328" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="329">
       <c r="A329"/>
       <c r="B329" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C329" t="n">
         <v>14</v>
@@ -10430,19 +9443,16 @@
         <v>0.94625276368264</v>
       </c>
       <c r="H329" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I329" t="s">
-        <v>22</v>
-      </c>
-      <c r="J329" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="330">
       <c r="A330"/>
       <c r="B330" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C330" t="n">
         <v>14</v>
@@ -10460,19 +9470,16 @@
         <v>0.934330263826498</v>
       </c>
       <c r="H330" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I330" t="s">
-        <v>18</v>
-      </c>
-      <c r="J330" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="331">
       <c r="A331"/>
       <c r="B331" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C331" t="n">
         <v>14</v>
@@ -10490,19 +9497,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H331" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I331" t="s">
-        <v>18</v>
-      </c>
-      <c r="J331" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="332">
       <c r="A332"/>
       <c r="B332" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C332" t="n">
         <v>14</v>
@@ -10520,19 +9524,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H332" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I332" t="s">
-        <v>22</v>
-      </c>
-      <c r="J332" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="333">
       <c r="A333"/>
       <c r="B333" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C333" t="n">
         <v>14</v>
@@ -10550,19 +9551,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H333" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I333" t="s">
-        <v>22</v>
-      </c>
-      <c r="J333" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="334">
       <c r="A334"/>
       <c r="B334" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C334" t="n">
         <v>14</v>
@@ -10580,19 +9578,16 @@
         <v>0.852007703632368</v>
       </c>
       <c r="H334" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I334" t="s">
-        <v>22</v>
-      </c>
-      <c r="J334" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="335">
       <c r="A335"/>
       <c r="B335" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C335" t="n">
         <v>15</v>
@@ -10610,19 +9605,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H335" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I335" t="s">
-        <v>17</v>
-      </c>
-      <c r="J335" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="336">
       <c r="A336"/>
       <c r="B336" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C336" t="n">
         <v>15</v>
@@ -10640,19 +9632,16 @@
         <v>0.859540943467457</v>
       </c>
       <c r="H336" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I336" t="s">
-        <v>17</v>
-      </c>
-      <c r="J336" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="337">
       <c r="A337"/>
       <c r="B337" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C337" t="n">
         <v>14</v>
@@ -10670,19 +9659,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H337" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I337" t="s">
-        <v>18</v>
-      </c>
-      <c r="J337" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="338">
       <c r="A338"/>
       <c r="B338" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C338" t="n">
         <v>14</v>
@@ -10700,19 +9686,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H338" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I338" t="s">
-        <v>18</v>
-      </c>
-      <c r="J338" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="339">
       <c r="A339"/>
       <c r="B339" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C339" t="n">
         <v>14</v>
@@ -10730,19 +9713,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H339" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I339" t="s">
-        <v>18</v>
-      </c>
-      <c r="J339" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="340">
       <c r="A340"/>
       <c r="B340" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C340" t="n">
         <v>15</v>
@@ -10760,19 +9740,16 @@
         <v>0.950301174011126</v>
       </c>
       <c r="H340" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I340" t="s">
-        <v>12</v>
-      </c>
-      <c r="J340" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="341">
       <c r="A341"/>
       <c r="B341" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C341" t="n">
         <v>15</v>
@@ -10790,19 +9767,16 @@
         <v>0.979753656625192</v>
       </c>
       <c r="H341" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I341" t="s">
-        <v>14</v>
-      </c>
-      <c r="J341" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="342">
       <c r="A342"/>
       <c r="B342" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C342" t="n">
         <v>14</v>
@@ -10820,19 +9794,16 @@
         <v>0.869333899732566</v>
       </c>
       <c r="H342" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I342" t="s">
-        <v>14</v>
-      </c>
-      <c r="J342" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="343">
       <c r="A343"/>
       <c r="B343" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C343" t="n">
         <v>15</v>
@@ -10850,19 +9821,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H343" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I343" t="s">
-        <v>17</v>
-      </c>
-      <c r="J343" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="344">
       <c r="A344"/>
       <c r="B344" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C344" t="n">
         <v>15</v>
@@ -10880,19 +9848,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H344" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I344" t="s">
-        <v>12</v>
-      </c>
-      <c r="J344" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="345">
       <c r="A345"/>
       <c r="B345" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C345" t="n">
         <v>15</v>
@@ -10910,19 +9875,16 @@
         <v>0.979753656625192</v>
       </c>
       <c r="H345" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I345" t="s">
-        <v>14</v>
-      </c>
-      <c r="J345" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="346">
       <c r="A346"/>
       <c r="B346" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C346" t="n">
         <v>14</v>
@@ -10940,19 +9902,16 @@
         <v>0.875502537632114</v>
       </c>
       <c r="H346" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I346" t="s">
-        <v>18</v>
-      </c>
-      <c r="J346" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="347">
       <c r="A347"/>
       <c r="B347" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C347" t="n">
         <v>14</v>
@@ -10970,19 +9929,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H347" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I347" t="s">
-        <v>18</v>
-      </c>
-      <c r="J347" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="348">
       <c r="A348"/>
       <c r="B348" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C348" t="n">
         <v>14</v>
@@ -11000,19 +9956,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H348" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I348" t="s">
-        <v>22</v>
-      </c>
-      <c r="J348" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="349">
       <c r="A349"/>
       <c r="B349" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C349" t="n">
         <v>14</v>
@@ -11030,19 +9983,16 @@
         <v>0.875502537632114</v>
       </c>
       <c r="H349" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I349" t="s">
-        <v>18</v>
-      </c>
-      <c r="J349" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="350">
       <c r="A350"/>
       <c r="B350" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C350" t="n">
         <v>14</v>
@@ -11060,19 +10010,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H350" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I350" t="s">
-        <v>22</v>
-      </c>
-      <c r="J350" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="351">
       <c r="A351"/>
       <c r="B351" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C351" t="n">
         <v>14</v>
@@ -11090,19 +10037,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H351" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I351" t="s">
-        <v>18</v>
-      </c>
-      <c r="J351" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="352">
       <c r="A352"/>
       <c r="B352" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C352" t="n">
         <v>15</v>
@@ -11120,19 +10064,16 @@
         <v>0.959699764598948</v>
       </c>
       <c r="H352" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I352" t="s">
-        <v>12</v>
-      </c>
-      <c r="J352" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="353">
       <c r="A353"/>
       <c r="B353" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C353" t="n">
         <v>15</v>
@@ -11150,19 +10091,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H353" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I353" t="s">
-        <v>12</v>
-      </c>
-      <c r="J353" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="354">
       <c r="A354"/>
       <c r="B354" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C354" t="n">
         <v>15</v>
@@ -11180,19 +10118,16 @@
         <v>0.8794603130259</v>
       </c>
       <c r="H354" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I354" t="s">
-        <v>14</v>
-      </c>
-      <c r="J354" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="355">
       <c r="A355"/>
       <c r="B355" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C355" t="n">
         <v>14</v>
@@ -11210,19 +10145,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H355" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I355" t="s">
-        <v>22</v>
-      </c>
-      <c r="J355" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="356">
       <c r="A356"/>
       <c r="B356" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C356" t="n">
         <v>14</v>
@@ -11240,19 +10172,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H356" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I356" t="s">
-        <v>18</v>
-      </c>
-      <c r="J356" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="357">
       <c r="A357"/>
       <c r="B357" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C357" t="n">
         <v>14</v>
@@ -11270,19 +10199,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H357" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I357" t="s">
-        <v>18</v>
-      </c>
-      <c r="J357" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="358">
       <c r="A358"/>
       <c r="B358" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C358" t="n">
         <v>15</v>
@@ -11300,19 +10226,16 @@
         <v>0.979844227761598</v>
       </c>
       <c r="H358" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I358" t="s">
-        <v>14</v>
-      </c>
-      <c r="J358" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="359">
       <c r="A359"/>
       <c r="B359" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C359" t="n">
         <v>15</v>
@@ -11330,19 +10253,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H359" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I359" t="s">
-        <v>17</v>
-      </c>
-      <c r="J359" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="360">
       <c r="A360"/>
       <c r="B360" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C360" t="n">
         <v>15</v>
@@ -11360,19 +10280,16 @@
         <v>0.979844227761598</v>
       </c>
       <c r="H360" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I360" t="s">
-        <v>14</v>
-      </c>
-      <c r="J360" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="361">
       <c r="A361"/>
       <c r="B361" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C361" t="n">
         <v>15</v>
@@ -11390,19 +10307,16 @@
         <v>0.969769876154569</v>
       </c>
       <c r="H361" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I361" t="s">
-        <v>17</v>
-      </c>
-      <c r="J361" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="362">
       <c r="A362"/>
       <c r="B362" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C362" t="n">
         <v>15</v>
@@ -11420,19 +10334,16 @@
         <v>1</v>
       </c>
       <c r="H362" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I362" t="s">
-        <v>28</v>
-      </c>
-      <c r="J362" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="363">
       <c r="A363"/>
       <c r="B363" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C363" t="n">
         <v>14</v>
@@ -11450,19 +10361,16 @@
         <v>0.94625276368264</v>
       </c>
       <c r="H363" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I363" t="s">
-        <v>22</v>
-      </c>
-      <c r="J363" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="364">
       <c r="A364"/>
       <c r="B364" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C364" t="n">
         <v>14</v>
@@ -11480,19 +10388,16 @@
         <v>0.934330263826498</v>
       </c>
       <c r="H364" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I364" t="s">
-        <v>18</v>
-      </c>
-      <c r="J364" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="365">
       <c r="A365"/>
       <c r="B365" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C365" t="n">
         <v>14</v>
@@ -11510,19 +10415,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H365" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I365" t="s">
-        <v>18</v>
-      </c>
-      <c r="J365" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="366">
       <c r="A366"/>
       <c r="B366" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C366" t="n">
         <v>14</v>
@@ -11540,19 +10442,16 @@
         <v>0.910918653071845</v>
       </c>
       <c r="H366" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I366" t="s">
-        <v>22</v>
-      </c>
-      <c r="J366" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="367">
       <c r="A367"/>
       <c r="B367" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C367" t="n">
         <v>14</v>
@@ -11570,19 +10469,16 @@
         <v>0.928531584478003</v>
       </c>
       <c r="H367" t="s">
+        <v>15</v>
+      </c>
+      <c r="I367" t="s">
         <v>16</v>
-      </c>
-      <c r="I367" t="s">
-        <v>17</v>
-      </c>
-      <c r="J367" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="368">
       <c r="A368"/>
       <c r="B368" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C368" t="n">
         <v>15</v>
@@ -11600,19 +10496,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H368" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I368" t="s">
-        <v>12</v>
-      </c>
-      <c r="J368" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="369">
       <c r="A369"/>
       <c r="B369" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C369" t="n">
         <v>14</v>
@@ -11630,19 +10523,16 @@
         <v>0.934330263826498</v>
       </c>
       <c r="H369" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I369" t="s">
-        <v>18</v>
-      </c>
-      <c r="J369" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="370">
       <c r="A370"/>
       <c r="B370" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C370" t="n">
         <v>14</v>
@@ -11660,19 +10550,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H370" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I370" t="s">
-        <v>22</v>
-      </c>
-      <c r="J370" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="371">
       <c r="A371"/>
       <c r="B371" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C371" t="n">
         <v>14</v>
@@ -11690,19 +10577,16 @@
         <v>0.94625276368264</v>
       </c>
       <c r="H371" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I371" t="s">
-        <v>22</v>
-      </c>
-      <c r="J371" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="372">
       <c r="A372"/>
       <c r="B372" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C372" t="n">
         <v>14</v>
@@ -11720,19 +10604,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H372" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I372" t="s">
-        <v>18</v>
-      </c>
-      <c r="J372" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="373">
       <c r="A373"/>
       <c r="B373" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C373" t="n">
         <v>15</v>
@@ -11750,19 +10631,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H373" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I373" t="s">
-        <v>17</v>
-      </c>
-      <c r="J373" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="374">
       <c r="A374"/>
       <c r="B374" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C374" t="n">
         <v>15</v>
@@ -11780,19 +10658,16 @@
         <v>0.949635304173862</v>
       </c>
       <c r="H374" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I374" t="s">
-        <v>12</v>
-      </c>
-      <c r="J374" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="375">
       <c r="A375"/>
       <c r="B375" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C375" t="n">
         <v>13</v>
@@ -11810,19 +10685,16 @@
         <v>0.964377780387274</v>
       </c>
       <c r="H375" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I375" t="s">
-        <v>22</v>
-      </c>
-      <c r="J375" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="376">
       <c r="A376"/>
       <c r="B376" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C376" t="n">
         <v>14</v>
@@ -11840,19 +10712,16 @@
         <v>0.988075108981028</v>
       </c>
       <c r="H376" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I376" t="s">
-        <v>28</v>
-      </c>
-      <c r="J376" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="377">
       <c r="A377"/>
       <c r="B377" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C377" t="n">
         <v>14</v>
@@ -11870,19 +10739,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H377" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I377" t="s">
-        <v>18</v>
-      </c>
-      <c r="J377" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="378">
       <c r="A378"/>
       <c r="B378" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C378" t="n">
         <v>14</v>
@@ -11900,19 +10766,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H378" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I378" t="s">
-        <v>22</v>
-      </c>
-      <c r="J378" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="379">
       <c r="A379"/>
       <c r="B379" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C379" t="n">
         <v>14</v>
@@ -11930,19 +10793,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H379" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I379" t="s">
-        <v>18</v>
-      </c>
-      <c r="J379" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="380">
       <c r="A380"/>
       <c r="B380" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C380" t="n">
         <v>14</v>
@@ -11960,19 +10820,16 @@
         <v>0.958369789371986</v>
       </c>
       <c r="H380" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I380" t="s">
-        <v>22</v>
-      </c>
-      <c r="J380" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="381">
       <c r="A381"/>
       <c r="B381" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C381" t="n">
         <v>15</v>
@@ -11990,19 +10847,16 @@
         <v>0.959518775459607</v>
       </c>
       <c r="H381" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I381" t="s">
-        <v>12</v>
-      </c>
-      <c r="J381" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="382">
       <c r="A382"/>
       <c r="B382" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C382" t="n">
         <v>15</v>
@@ -12020,19 +10874,16 @@
         <v>0.959699764598948</v>
       </c>
       <c r="H382" t="s">
+        <v>26</v>
+      </c>
+      <c r="I382" t="s">
         <v>27</v>
-      </c>
-      <c r="I382" t="s">
-        <v>28</v>
-      </c>
-      <c r="J382" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="383">
       <c r="A383"/>
       <c r="B383" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C383" t="n">
         <v>15</v>
@@ -12050,19 +10901,16 @@
         <v>0.959699764598948</v>
       </c>
       <c r="H383" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I383" t="s">
-        <v>12</v>
-      </c>
-      <c r="J383" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="384">
       <c r="A384"/>
       <c r="B384" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C384" t="n">
         <v>13</v>
@@ -12080,19 +10928,16 @@
         <v>0.964377780387274</v>
       </c>
       <c r="H384" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I384" t="s">
-        <v>22</v>
-      </c>
-      <c r="J384" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="385">
       <c r="A385"/>
       <c r="B385" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C385" t="n">
         <v>15</v>
@@ -12110,19 +10955,16 @@
         <v>0.979753656625192</v>
       </c>
       <c r="H385" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I385" t="s">
-        <v>14</v>
-      </c>
-      <c r="J385" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="386">
       <c r="A386"/>
       <c r="B386" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C386" t="n">
         <v>15</v>
@@ -12140,19 +10982,16 @@
         <v>0.969634067313828</v>
       </c>
       <c r="H386" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I386" t="s">
-        <v>28</v>
-      </c>
-      <c r="J386" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="387">
       <c r="A387"/>
       <c r="B387" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C387" t="n">
         <v>15</v>
@@ -12170,19 +11009,16 @@
         <v>0.969769876154569</v>
       </c>
       <c r="H387" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I387" t="s">
-        <v>17</v>
-      </c>
-      <c r="J387" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="388">
       <c r="A388"/>
       <c r="B388" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C388" t="n">
         <v>15</v>
@@ -12200,19 +11036,16 @@
         <v>0.979753656625192</v>
       </c>
       <c r="H388" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I388" t="s">
-        <v>14</v>
-      </c>
-      <c r="J388" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="389">
       <c r="A389"/>
       <c r="B389" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C389" t="n">
         <v>15</v>
@@ -12230,19 +11063,16 @@
         <v>0.979844227761598</v>
       </c>
       <c r="H389" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I389" t="s">
-        <v>14</v>
-      </c>
-      <c r="J389" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="390">
       <c r="A390"/>
       <c r="B390" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C390" t="n">
         <v>14</v>
@@ -12260,19 +11090,16 @@
         <v>0.988075108981028</v>
       </c>
       <c r="H390" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I390" t="s">
-        <v>28</v>
-      </c>
-      <c r="J390" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="391">
       <c r="A391"/>
       <c r="B391" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C391" t="n">
         <v>15</v>
@@ -12290,19 +11117,16 @@
         <v>0.989921406880978</v>
       </c>
       <c r="H391" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I391" t="s">
-        <v>28</v>
-      </c>
-      <c r="J391" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="392">
       <c r="A392"/>
       <c r="B392" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C392" t="n">
         <v>15</v>
@@ -12320,19 +11144,16 @@
         <v>0.989921406880978</v>
       </c>
       <c r="H392" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I392" t="s">
-        <v>14</v>
-      </c>
-      <c r="J392" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="393">
       <c r="A393"/>
       <c r="B393" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C393" t="n">
         <v>15</v>
@@ -12350,19 +11171,16 @@
         <v>1</v>
       </c>
       <c r="H393" t="s">
+        <v>10</v>
+      </c>
+      <c r="I393" t="s">
         <v>11</v>
-      </c>
-      <c r="I393" t="s">
-        <v>12</v>
-      </c>
-      <c r="J393" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="394">
       <c r="A394"/>
       <c r="B394" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C394" t="n">
         <v>13</v>
@@ -12380,19 +11198,16 @@
         <v>0.992873609475608</v>
       </c>
       <c r="H394" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I394" t="s">
-        <v>18</v>
-      </c>
-      <c r="J394" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="395">
       <c r="A395"/>
       <c r="B395" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C395" t="n">
         <v>15</v>
@@ -12410,19 +11225,16 @@
         <v>1</v>
       </c>
       <c r="H395" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I395" t="s">
-        <v>28</v>
-      </c>
-      <c r="J395" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="396">
       <c r="A396"/>
       <c r="B396" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C396" t="n">
         <v>15</v>
@@ -12440,19 +11252,16 @@
         <v>1</v>
       </c>
       <c r="H396" t="s">
+        <v>10</v>
+      </c>
+      <c r="I396" t="s">
         <v>11</v>
-      </c>
-      <c r="I396" t="s">
-        <v>12</v>
-      </c>
-      <c r="J396" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="397">
       <c r="A397"/>
       <c r="B397" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C397" t="n">
         <v>15</v>
@@ -12470,13 +11279,10 @@
         <v>1</v>
       </c>
       <c r="H397" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I397" t="s">
-        <v>28</v>
-      </c>
-      <c r="J397" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -12495,45 +11301,45 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
         <v>33</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>35</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>36</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>37</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>38</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>39</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>40</v>
-      </c>
-      <c r="J1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
         <v>42</v>
       </c>
-      <c r="C2" t="s">
-        <v>43</v>
-      </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -12549,21 +11355,21 @@
       </c>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
         <v>45</v>
       </c>
-      <c r="C3" t="s">
-        <v>46</v>
-      </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -12579,21 +11385,21 @@
       </c>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
         <v>48</v>
       </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -12609,21 +11415,21 @@
       </c>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
         <v>51</v>
       </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -12639,21 +11445,21 @@
       </c>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -12669,21 +11475,21 @@
       </c>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -12699,21 +11505,21 @@
       </c>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
         <v>58</v>
       </c>
-      <c r="C8" t="s">
-        <v>59</v>
-      </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -12729,21 +11535,21 @@
       </c>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
         <v>61</v>
       </c>
-      <c r="C9" t="s">
-        <v>62</v>
-      </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -12759,21 +11565,21 @@
       </c>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
         <v>64</v>
       </c>
-      <c r="C10" t="s">
-        <v>65</v>
-      </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -12789,21 +11595,21 @@
       </c>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
         <v>67</v>
       </c>
-      <c r="C11" t="s">
-        <v>68</v>
-      </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12819,21 +11625,21 @@
       </c>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
         <v>70</v>
       </c>
-      <c r="C12" t="s">
-        <v>71</v>
-      </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -12849,7 +11655,7 @@
       </c>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
